--- a/output/VAT transaction lines Q2'26.xlsx
+++ b/output/VAT transaction lines Q2'26.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6053,7 +6053,11 @@
           <t>Commission Hotels</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
       <c r="F169" t="inlineStr"/>
       <c r="G169" t="n">
         <v>-6591.13</v>
@@ -6203,172 +6207,196 @@
           <t>Commission Hotels</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="n">
-        <v>-11306.96</v>
+        <v>-498.39</v>
       </c>
       <c r="H174" t="n">
-        <v>256</v>
+        <v>12</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>UEU</t>
+          <t>PAS</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>European Reverse Charge</t>
+          <t>Paid on behalf of customer</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>40751</t>
+          <t>82002</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Outsourced personnel - IT Team</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr"/>
+          <t>Commission Hotels</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>4B, 5B</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>5150</v>
+        <v>-2304</v>
       </c>
       <c r="H175" t="n">
-        <v>1</v>
+        <v>77</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>UEU</t>
+          <t>PAS</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>European Reverse Charge</t>
+          <t>Paid on behalf of customer</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>40755</t>
+          <t>82002</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Outsourced personnel - Product Team</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr"/>
+          <t>Commission Hotels</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>4B, 5B</t>
+          <t>1E</t>
         </is>
       </c>
       <c r="G176" t="n">
-        <v>4200</v>
+        <v>-298</v>
       </c>
       <c r="H176" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>UN9</t>
+          <t>PAS</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Domestic Purchases Low (9%)</t>
+          <t>Paid on behalf of customer</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>82002</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Vat Receivable (low)</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
+          <t>Commission Hotels</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
       <c r="G177" t="n">
-        <v>222.35</v>
+        <v>-8206.57</v>
       </c>
       <c r="H177" t="n">
-        <v>2</v>
+        <v>150</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>UN9</t>
+          <t>UEU</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Domestic Purchases Low (9%)</t>
+          <t>European Reverse Charge</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>40751</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Other Personnel Costs</t>
+          <t>Outsourced personnel - IT Team</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>5B</t>
+          <t>4B, 5B</t>
         </is>
       </c>
       <c r="G178" t="n">
-        <v>2470.62</v>
+        <v>5150</v>
       </c>
       <c r="H178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>UNL</t>
+          <t>UEU</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Domestic Purchases High (21%)</t>
+          <t>European Reverse Charge</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>40755</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Vat Receivable (high)</t>
+          <t>Outsourced personnel - Product Team</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>4B, 5B</t>
+        </is>
+      </c>
       <c r="G179" t="n">
-        <v>423.5</v>
+        <v>4200</v>
       </c>
       <c r="H179" t="n">
         <v>1</v>
@@ -6377,66 +6405,62 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>UNL</t>
+          <t>UN9</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Domestic Purchases High (21%)</t>
+          <t>Domestic Purchases Low (9%)</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Other Personnel Costs</t>
+          <t>Vat Receivable (low)</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>5B</t>
-        </is>
-      </c>
+      <c r="F180" t="inlineStr"/>
       <c r="G180" t="n">
-        <v>2016.67</v>
+        <v>222.35</v>
       </c>
       <c r="H180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>UWW</t>
+          <t>UN9</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Non-EU Purchases Reverse Charge</t>
+          <t>Domestic Purchases Low (9%)</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Cashback accruals</t>
+          <t>Other Personnel Costs</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>4A, 5B</t>
+          <t>5B</t>
         </is>
       </c>
       <c r="G181" t="n">
-        <v>14490</v>
+        <v>2470.62</v>
       </c>
       <c r="H181" t="n">
         <v>2</v>
@@ -6445,66 +6469,62 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>UWW</t>
+          <t>UNL</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Non-EU Purchases Reverse Charge</t>
+          <t>Domestic Purchases High (21%)</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>40751</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Outsourced personnel - IT Team</t>
+          <t>Vat Receivable (high)</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>4A, 5B</t>
-        </is>
-      </c>
+      <c r="F182" t="inlineStr"/>
       <c r="G182" t="n">
-        <v>31075</v>
+        <v>423.5</v>
       </c>
       <c r="H182" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>UWW</t>
+          <t>UNL</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Non-EU Purchases Reverse Charge</t>
+          <t>Domestic Purchases High (21%)</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>40752</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Outsourced personnel - Finance Team</t>
+          <t>Other Personnel Costs</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
-          <t>4A, 5B</t>
+          <t>5B</t>
         </is>
       </c>
       <c r="G183" t="n">
-        <v>1750</v>
+        <v>2016.67</v>
       </c>
       <c r="H183" t="n">
         <v>1</v>
@@ -6523,12 +6543,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>40754</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Outsourced personnel - Operations Team</t>
+          <t>Cashback accruals</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -6538,10 +6558,10 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>6451.69</v>
+        <v>14490</v>
       </c>
       <c r="H184" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -6557,12 +6577,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>40755</t>
+          <t>40751</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Outsourced personnel - Product Team</t>
+          <t>Outsourced personnel - IT Team</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -6572,10 +6592,10 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>10400</v>
+        <v>31075</v>
       </c>
       <c r="H185" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="186">
@@ -6591,12 +6611,12 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>40757</t>
+          <t>40752</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Outsourced personnel - Customer Success Team</t>
+          <t>Outsourced personnel - Finance Team</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -6606,10 +6626,10 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>3855</v>
+        <v>1750</v>
       </c>
       <c r="H186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187">
@@ -6625,12 +6645,12 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>40754</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Conferences and exhibitions</t>
+          <t>Outsourced personnel - Operations Team</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
@@ -6640,10 +6660,10 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>12877.03</v>
+        <v>6451.69</v>
       </c>
       <c r="H187" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="188">
@@ -6659,12 +6679,12 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>40755</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Advisory costs</t>
+          <t>Outsourced personnel - Product Team</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
@@ -6674,9 +6694,111 @@
         </is>
       </c>
       <c r="G188" t="n">
+        <v>10400</v>
+      </c>
+      <c r="H188" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>UWW</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Non-EU Purchases Reverse Charge</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>40757</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Outsourced personnel - Customer Success Team</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>4A, 5B</t>
+        </is>
+      </c>
+      <c r="G189" t="n">
+        <v>3855</v>
+      </c>
+      <c r="H189" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>UWW</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Non-EU Purchases Reverse Charge</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>4340</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Conferences and exhibitions</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>4A, 5B</t>
+        </is>
+      </c>
+      <c r="G190" t="n">
+        <v>12877.03</v>
+      </c>
+      <c r="H190" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>UWW</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Non-EU Purchases Reverse Charge</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>4856</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Advisory costs</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>4A, 5B</t>
+        </is>
+      </c>
+      <c r="G191" t="n">
         <v>6571.35</v>
       </c>
-      <c r="H188" t="n">
+      <c r="H191" t="n">
         <v>1</v>
       </c>
     </row>

--- a/output/VAT transaction lines Q2'26.xlsx
+++ b/output/VAT transaction lines Q2'26.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H191"/>
+  <dimension ref="A1:H203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1404,10 +1404,10 @@
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>-6148.71</v>
+        <v>-6090.68</v>
       </c>
       <c r="H29" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30">
@@ -1423,21 +1423,29 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>9040</t>
+          <t>8091</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FX difference - negative</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+          <t>Minimum booking fee</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
       <c r="G30" t="n">
-        <v>13.03</v>
+        <v>-58.03</v>
       </c>
       <c r="H30" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -1453,51 +1461,51 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>9041</t>
+          <t>9040</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FX difference - positive</t>
+          <t>FX difference - negative</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>15.75</v>
+        <v>13.03</v>
       </c>
       <c r="H31" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>102</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Purchases outside EU</t>
+          <t>Commission Non EU</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>9041</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Deposits to suppliers</t>
+          <t>FX difference - positive</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>27500</v>
+        <v>15.75</v>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33">
@@ -1513,21 +1521,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Vat Receivable (high)</t>
+          <t>Deposits to suppliers</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>84279.99000000001</v>
+        <v>27500</v>
       </c>
       <c r="H33" t="n">
-        <v>83</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -1543,18 +1551,18 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Purchases outside EU</t>
+          <t>Vat Receivable (high)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>-84279.99000000001</v>
+        <v>84279.99000000001</v>
       </c>
       <c r="H34" t="n">
         <v>83</v>
@@ -1573,21 +1581,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cashback accruals</t>
+          <t>Purchases outside EU</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>25867.98</v>
+        <v>-84279.99000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36">
@@ -1603,25 +1611,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>40751</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Outsourced personnel - IT Team</t>
+          <t>Cashback accruals</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>4A, 5B</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>184781.67</v>
+        <v>25867.98</v>
       </c>
       <c r="H36" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -1637,12 +1641,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>40754</t>
+          <t>40751</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Outsourced personnel - Operations Team</t>
+          <t>Outsourced personnel - IT Team</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1652,10 +1656,10 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>33615.89</v>
+        <v>184781.67</v>
       </c>
       <c r="H37" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38">
@@ -1671,12 +1675,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>40755</t>
+          <t>40754</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Outsourced personnel - Product Team</t>
+          <t>Outsourced personnel - Operations Team</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -1686,10 +1690,10 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>9600</v>
+        <v>33615.89</v>
       </c>
       <c r="H38" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39">
@@ -1705,12 +1709,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>40756</t>
+          <t>40755</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Outsourced personnel - Sales Team</t>
+          <t>Outsourced personnel - Product Team</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1720,7 +1724,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>15000</v>
+        <v>9600</v>
       </c>
       <c r="H39" t="n">
         <v>3</v>
@@ -1739,12 +1743,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>40756</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Conferences and exhibitions</t>
+          <t>Outsourced personnel - Sales Team</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1754,10 +1758,10 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>2073.29</v>
+        <v>15000</v>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -1773,12 +1777,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>4821</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Subscriptions product team</t>
+          <t>Conferences and exhibitions</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1788,10 +1792,10 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1807.84</v>
+        <v>2073.29</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -1807,12 +1811,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>4825</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Subscriptions Sales</t>
+          <t>Subscriptions product team</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1822,7 +1826,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>686.05</v>
+        <v>1807.84</v>
       </c>
       <c r="H42" t="n">
         <v>1</v>
@@ -1841,12 +1845,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Digital Marketing expenses</t>
+          <t>Subscriptions Sales</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1856,7 +1860,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>229.8</v>
+        <v>686.05</v>
       </c>
       <c r="H43" t="n">
         <v>1</v>
@@ -1875,12 +1879,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Subscriptions Operations</t>
+          <t>Digital Marketing expenses</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -1890,7 +1894,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>3958.5</v>
+        <v>229.8</v>
       </c>
       <c r="H44" t="n">
         <v>1</v>
@@ -1909,12 +1913,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>7223</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Incidentals, errors, ADM penalties</t>
+          <t>Subscriptions Operations</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -1924,7 +1928,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>255.86</v>
+        <v>3958.5</v>
       </c>
       <c r="H45" t="n">
         <v>1</v>
@@ -1943,22 +1947,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>7223</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Turnover Saas montly fees</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
+          <t>Incidentals, errors, ADM penalties</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>4A, 5B</t>
+        </is>
+      </c>
       <c r="G46" t="n">
-        <v>-17.26</v>
+        <v>255.86</v>
       </c>
       <c r="H46" t="n">
         <v>1</v>
@@ -1977,51 +1981,55 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>9040</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>FX difference - negative</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
+          <t>Turnover Saas montly fees</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
-        <v>159.3</v>
+        <v>-17.26</v>
       </c>
       <c r="H47" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sales Margin 21% NL</t>
+          <t>Purchases outside EU</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>80003</t>
+          <t>9040</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Turnover Other Products</t>
+          <t>FX difference - negative</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
-        <v>-1046.59</v>
+        <v>159.3</v>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49">
@@ -2037,26 +2045,18 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>80003</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Turnover Saas montly fees</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>1A</t>
-        </is>
-      </c>
+          <t>Turnover Other Products</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
-        <v>-7332.21</v>
+        <v>-1046.59</v>
       </c>
       <c r="H49" t="n">
         <v>3</v>
@@ -2075,12 +2075,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>81003</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Markup Other Products</t>
+          <t>Turnover Saas montly fees</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>-75</v>
+        <v>-7332.21</v>
       </c>
       <c r="H50" t="n">
         <v>3</v>
@@ -2103,31 +2103,39 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ticket sales NL 0%</t>
+          <t>Sales Margin 21% NL</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>81003</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Bookings cost of sale suspense</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+          <t>Markup Other Products</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
       <c r="G51" t="n">
-        <v>3285155.61</v>
+        <v>-75</v>
       </c>
       <c r="H51" t="n">
-        <v>55</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -2143,21 +2151,21 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Unexpected cost to be reconciled</t>
+          <t>Bookings cost of sale suspense</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
-        <v>240.51</v>
+        <v>3285155.61</v>
       </c>
       <c r="H52" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
     </row>
     <row r="53">
@@ -2173,21 +2181,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Cashback accruals</t>
+          <t>Unexpected cost to be reconciled</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
-        <v>-25320</v>
+        <v>240.51</v>
       </c>
       <c r="H53" t="n">
-        <v>607</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54">
@@ -2203,21 +2211,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Suspense - research payments manually</t>
+          <t>Cashback accruals</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
-        <v>2749890.76</v>
+        <v>-25320</v>
       </c>
       <c r="H54" t="n">
-        <v>3</v>
+        <v>607</v>
       </c>
     </row>
     <row r="55">
@@ -2233,29 +2241,21 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Consolidator fees costs</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+          <t>Suspense - research payments manually</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
-        <v>20903.57</v>
+        <v>2749890.76</v>
       </c>
       <c r="H55" t="n">
-        <v>9648</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -2271,21 +2271,25 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>80001</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Turnover flights</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
+          <t>Consolidator fees costs</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
-        <v>-4476797.29</v>
+        <v>20903.57</v>
       </c>
       <c r="H56" t="n">
-        <v>3659</v>
+        <v>9648</v>
       </c>
     </row>
     <row r="57">
@@ -2301,21 +2305,21 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>80003</t>
+          <t>80001</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Turnover Other Products</t>
+          <t>Turnover flights</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
-        <v>-35270.21</v>
+        <v>-4476797.29</v>
       </c>
       <c r="H57" t="n">
-        <v>220</v>
+        <v>3659</v>
       </c>
     </row>
     <row r="58">
@@ -2331,29 +2335,21 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>81001</t>
+          <t>80003</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Markup Flights</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+          <t>Turnover Other Products</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
-        <v>-196950.74</v>
+        <v>-35270.21</v>
       </c>
       <c r="H58" t="n">
-        <v>3575</v>
+        <v>220</v>
       </c>
     </row>
     <row r="59">
@@ -2369,12 +2365,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>81003</t>
+          <t>81001</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Markup Other Products</t>
+          <t>Markup Flights</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2382,16 +2378,12 @@
           <t>Margin</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
-        <v>-3297.74</v>
+        <v>-6083</v>
       </c>
       <c r="H59" t="n">
-        <v>216</v>
+        <v>155</v>
       </c>
     </row>
     <row r="60">
@@ -2407,12 +2399,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>81001</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>FX markup</t>
+          <t>Markup Flights</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2426,10 +2418,10 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>-7945.92</v>
+        <v>-190867.74</v>
       </c>
       <c r="H60" t="n">
-        <v>602</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="61">
@@ -2445,12 +2437,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>81003</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Consolidator markup</t>
+          <t>Markup Other Products</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2458,16 +2450,12 @@
           <t>Margin</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
-        <v>-2843.07</v>
+        <v>-308.32</v>
       </c>
       <c r="H61" t="n">
-        <v>1445</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62">
@@ -2483,12 +2471,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>81003</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>GDS incentive compensation markup</t>
+          <t>Markup Other Products</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2498,14 +2486,14 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1E</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>-8804.530000000001</v>
+        <v>-2989.42</v>
       </c>
       <c r="H62" t="n">
-        <v>1262</v>
+        <v>197</v>
       </c>
     </row>
     <row r="63">
@@ -2521,21 +2509,25 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Revenue from rebooking price differences</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
+          <t>FX markup</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>-653.14</v>
+        <v>-7945.92</v>
       </c>
       <c r="H63" t="n">
-        <v>5</v>
+        <v>602</v>
       </c>
     </row>
     <row r="64">
@@ -2551,21 +2543,25 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Positive variance - gain</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr"/>
+          <t>Consolidator markup</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
-        <v>-2272.46</v>
+        <v>-75.84999999999999</v>
       </c>
       <c r="H64" t="n">
-        <v>2362</v>
+        <v>63</v>
       </c>
     </row>
     <row r="65">
@@ -2581,187 +2577,191 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>9060</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Rounding differences</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
+          <t>Consolidator markup</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>-2767.22</v>
       </c>
       <c r="H65" t="n">
-        <v>2</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NL VAT 21% - VAT high rate, excluding (purchase)</t>
+          <t>Ticket sales NL 0%</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Vat Receivable (high)</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
+          <t>GDS incentive compensation markup</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
-        <v>20339.86</v>
+        <v>-155.74</v>
       </c>
       <c r="H66" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NL VAT 21% - VAT high rate, excluding (purchase)</t>
+          <t>Ticket sales NL 0%</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Management Fee</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
+          <t>GDS incentive compensation markup</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>5B</t>
+          <t>1E</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>32766</v>
+        <v>-8648.790000000001</v>
       </c>
       <c r="H67" t="n">
-        <v>3</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NL VAT 21% - VAT high rate, excluding (purchase)</t>
+          <t>Ticket sales NL 0%</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Insurance costs Illness</t>
+          <t>Revenue from rebooking price differences</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>5B</t>
-        </is>
-      </c>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
-        <v>425.33</v>
+        <v>-653.14</v>
       </c>
       <c r="H68" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NL VAT 21% - VAT high rate, excluding (purchase)</t>
+          <t>Ticket sales NL 0%</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Other Personnel Costs</t>
+          <t>Positive variance - gain</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>5B</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
-        <v>3344.18</v>
+        <v>-2272.46</v>
       </c>
       <c r="H69" t="n">
-        <v>3</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NL VAT 21% - VAT high rate, excluding (purchase)</t>
+          <t>Ticket sales NL 0%</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>9060</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Recruitment fees</t>
+          <t>Rounding differences</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>5B</t>
-        </is>
-      </c>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
-        <v>194.02</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -2777,25 +2777,21 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Office rent</t>
+          <t>Vat Receivable (high)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>5B</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
-        <v>32963.76</v>
+        <v>20339.86</v>
       </c>
       <c r="H71" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="72">
@@ -2811,12 +2807,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Cleaning Fee</t>
+          <t>Management Fee</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -2826,7 +2822,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>1110.27</v>
+        <v>32766</v>
       </c>
       <c r="H72" t="n">
         <v>3</v>
@@ -2845,12 +2841,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Conferences and exhibitions</t>
+          <t>Insurance costs Illness</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -2860,10 +2856,10 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>20421.49</v>
+        <v>425.33</v>
       </c>
       <c r="H73" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -2879,21 +2875,25 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>4510</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Legal costs</t>
+          <t>Other Personnel Costs</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>5B</t>
+        </is>
+      </c>
       <c r="G74" t="n">
-        <v>-2608.95</v>
+        <v>3344.18</v>
       </c>
       <c r="H74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -2909,12 +2909,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>4510</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Legal costs</t>
+          <t>Recruitment fees</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -2924,10 +2924,10 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>7987.11</v>
+        <v>194.02</v>
       </c>
       <c r="H75" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -2943,12 +2943,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>48204</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>IT Data feeds</t>
+          <t>Office rent</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -2958,10 +2958,10 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>2110</v>
+        <v>32963.76</v>
       </c>
       <c r="H76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>4140</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Subscriptions finance</t>
+          <t>Cleaning Fee</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -2992,10 +2992,10 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>2904</v>
+        <v>1110.27</v>
       </c>
       <c r="H77" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
@@ -3011,12 +3011,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Digital Marketing expenses</t>
+          <t>Conferences and exhibitions</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -3026,10 +3026,10 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>202.59</v>
+        <v>20421.49</v>
       </c>
       <c r="H78" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
@@ -3045,25 +3045,21 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Subscriptions General</t>
+          <t>Legal costs</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>5B</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
-        <v>2970</v>
+        <v>-2608.95</v>
       </c>
       <c r="H79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -3079,12 +3075,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Telephone and fax costs</t>
+          <t>Legal costs</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -3094,10 +3090,10 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>132.68</v>
+        <v>7987.11</v>
       </c>
       <c r="H80" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
@@ -3113,12 +3109,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>4853</t>
+          <t>48204</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Administration costs Acountant</t>
+          <t>IT Data feeds</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -3128,10 +3124,10 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>1306.25</v>
+        <v>2110</v>
       </c>
       <c r="H81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -3147,21 +3143,25 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>4823</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Advisory costs</t>
+          <t>Subscriptions finance</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>5B</t>
+        </is>
+      </c>
       <c r="G82" t="n">
-        <v>-12000</v>
+        <v>2904</v>
       </c>
       <c r="H82" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Advisory costs</t>
+          <t>Digital Marketing expenses</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>2407.5</v>
+        <v>202.59</v>
       </c>
       <c r="H83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -3211,21 +3211,25 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Various office expense</t>
+          <t>Subscriptions General</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>5B</t>
+        </is>
+      </c>
       <c r="G84" t="n">
-        <v>-82.56</v>
+        <v>2970</v>
       </c>
       <c r="H84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -3241,12 +3245,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Various office expense</t>
+          <t>Telephone and fax costs</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -3256,164 +3260,172 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>302.68</v>
+        <v>132.68</v>
       </c>
       <c r="H85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ticket sales outside EU</t>
+          <t>NL VAT 21% - VAT high rate, excluding (purchase)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>4853</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Cashback accruals</t>
+          <t>Administration costs Acountant</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>5B</t>
+        </is>
+      </c>
       <c r="G86" t="n">
-        <v>-26775.54</v>
+        <v>1306.25</v>
       </c>
       <c r="H86" t="n">
-        <v>556</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ticket sales outside EU</t>
+          <t>NL VAT 21% - VAT high rate, excluding (purchase)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>80001</t>
+          <t>4856</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Turnover flights</t>
+          <t>Advisory costs</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="n">
-        <v>-6900347.94</v>
+        <v>-12000</v>
       </c>
       <c r="H87" t="n">
-        <v>6123</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ticket sales outside EU</t>
+          <t>NL VAT 21% - VAT high rate, excluding (purchase)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>80002</t>
+          <t>4856</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Turnover Hotels</t>
+          <t>Advisory costs</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>5B</t>
+        </is>
+      </c>
       <c r="G88" t="n">
-        <v>-286249.07</v>
+        <v>2407.5</v>
       </c>
       <c r="H88" t="n">
-        <v>721</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ticket sales outside EU</t>
+          <t>NL VAT 21% - VAT high rate, excluding (purchase)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>80003</t>
+          <t>4875</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Turnover Other Products</t>
+          <t>Various office expense</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
-        <v>-66019.77</v>
+        <v>-82.56</v>
       </c>
       <c r="H89" t="n">
-        <v>427</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ticket sales outside EU</t>
+          <t>NL VAT 21% - VAT high rate, excluding (purchase)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>4875</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Turnover Saas montly fees</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr"/>
+          <t>Various office expense</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>5B</t>
+        </is>
+      </c>
       <c r="G90" t="n">
-        <v>-283972.49</v>
+        <v>302.68</v>
       </c>
       <c r="H90" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -3429,25 +3441,21 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>81001</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Markup Flights</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
+          <t>Cashback accruals</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
-        <v>-342590.31</v>
+        <v>-26775.54</v>
       </c>
       <c r="H91" t="n">
-        <v>5991</v>
+        <v>556</v>
       </c>
     </row>
     <row r="92">
@@ -3463,25 +3471,21 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>81002</t>
+          <t>80001</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Markup Hotels</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
+          <t>Turnover flights</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
-        <v>-39581.77</v>
+        <v>-6900347.94</v>
       </c>
       <c r="H92" t="n">
-        <v>720</v>
+        <v>6123</v>
       </c>
     </row>
     <row r="93">
@@ -3497,25 +3501,21 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>81003</t>
+          <t>80002</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Markup Other Products</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
+          <t>Turnover Hotels</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="n">
-        <v>-9536.469999999999</v>
+        <v>-286249.07</v>
       </c>
       <c r="H93" t="n">
-        <v>451</v>
+        <v>721</v>
       </c>
     </row>
     <row r="94">
@@ -3531,25 +3531,21 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>80003</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>FX markup</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
+          <t>Turnover Other Products</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="n">
-        <v>-28212.67</v>
+        <v>-66019.77</v>
       </c>
       <c r="H94" t="n">
-        <v>4699</v>
+        <v>427</v>
       </c>
     </row>
     <row r="95">
@@ -3565,12 +3561,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Consolidator markup</t>
+          <t>Turnover Saas montly fees</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3580,10 +3576,10 @@
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
-        <v>-5684.83</v>
+        <v>-283972.49</v>
       </c>
       <c r="H95" t="n">
-        <v>2424</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96">
@@ -3599,12 +3595,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>81001</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>GDS incentive compensation markup</t>
+          <t>Markup Flights</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3614,10 +3610,10 @@
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
-        <v>-15823.69</v>
+        <v>-330588.97</v>
       </c>
       <c r="H96" t="n">
-        <v>1960</v>
+        <v>5549</v>
       </c>
     </row>
     <row r="97">
@@ -3633,21 +3629,29 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>81001</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Revenue from rebooking price differences</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
+          <t>Markup Flights</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G97" t="n">
-        <v>-6031.14</v>
+        <v>-12001.34</v>
       </c>
       <c r="H97" t="n">
-        <v>45</v>
+        <v>442</v>
       </c>
     </row>
     <row r="98">
@@ -3663,21 +3667,25 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>81002</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Positive variance - gain</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr"/>
+          <t>Markup Hotels</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
-        <v>-4233.86</v>
+        <v>-38296.77</v>
       </c>
       <c r="H98" t="n">
-        <v>4915</v>
+        <v>659</v>
       </c>
     </row>
     <row r="99">
@@ -3693,21 +3701,29 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>9040</t>
+          <t>81002</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>FX difference - negative</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
+          <t>Markup Hotels</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
       <c r="G99" t="n">
-        <v>47.9</v>
+        <v>-1285</v>
       </c>
       <c r="H99" t="n">
-        <v>18</v>
+        <v>61</v>
       </c>
     </row>
     <row r="100">
@@ -3723,162 +3739,190 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>9041</t>
+          <t>81003</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>FX difference - positive</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr"/>
+          <t>Markup Other Products</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="n">
-        <v>-242.4</v>
+        <v>-8642.48</v>
       </c>
       <c r="H100" t="n">
-        <v>35</v>
+        <v>376</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Ticket Sales within EU</t>
+          <t>Ticket sales outside EU</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>81003</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Cashback accruals</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
+          <t>Markup Other Products</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
       <c r="G101" t="n">
-        <v>-154645.16</v>
+        <v>-893.99</v>
       </c>
       <c r="H101" t="n">
-        <v>1061</v>
+        <v>75</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Ticket Sales within EU</t>
+          <t>Ticket sales outside EU</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>80001</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Turnover flights</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr"/>
+          <t>FX markup</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="n">
-        <v>-7865577.82</v>
+        <v>-28212.67</v>
       </c>
       <c r="H102" t="n">
-        <v>7354</v>
+        <v>4699</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Ticket Sales within EU</t>
+          <t>Ticket sales outside EU</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>80002</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Turnover Hotels</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr"/>
+          <t>Consolidator markup</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="n">
-        <v>-301706.24</v>
+        <v>-5371.99</v>
       </c>
       <c r="H103" t="n">
-        <v>954</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ticket Sales within EU</t>
+          <t>Ticket sales outside EU</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>80003</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Turnover Other Products</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
+          <t>Consolidator markup</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G104" t="n">
-        <v>-131837.53</v>
+        <v>-312.84</v>
       </c>
       <c r="H104" t="n">
-        <v>695</v>
+        <v>205</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Ticket Sales within EU</t>
+          <t>Ticket sales outside EU</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Turnover Saas montly fees</t>
+          <t>GDS incentive compensation markup</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -3886,37 +3930,33 @@
           <t>Margin</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
+      <c r="F105" t="inlineStr"/>
       <c r="G105" t="n">
-        <v>-2409</v>
+        <v>-15086.9</v>
       </c>
       <c r="H105" t="n">
-        <v>1</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ticket Sales within EU</t>
+          <t>Ticket sales outside EU</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>GDS incentives</t>
+          <t>GDS incentive compensation markup</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -3926,166 +3966,134 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>1E</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>-209365.74</v>
+        <v>-736.79</v>
       </c>
       <c r="H106" t="n">
-        <v>5</v>
+        <v>130</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ticket Sales within EU</t>
+          <t>Ticket sales outside EU</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>81001</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Markup Flights</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+          <t>Revenue from rebooking price differences</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
       <c r="G107" t="n">
-        <v>-39622.62</v>
+        <v>-6031.14</v>
       </c>
       <c r="H107" t="n">
-        <v>273</v>
+        <v>45</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Ticket Sales within EU</t>
+          <t>Ticket sales outside EU</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>81001</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Markup Flights</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
+          <t>Positive variance - gain</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
       <c r="G108" t="n">
-        <v>-429204.31</v>
+        <v>-4233.86</v>
       </c>
       <c r="H108" t="n">
-        <v>6925</v>
+        <v>4915</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ticket Sales within EU</t>
+          <t>Ticket sales outside EU</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>81002</t>
+          <t>9040</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Markup Hotels</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+          <t>FX difference - negative</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
       <c r="G109" t="n">
-        <v>-3855.64</v>
+        <v>47.9</v>
       </c>
       <c r="H109" t="n">
-        <v>109</v>
+        <v>18</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Ticket Sales within EU</t>
+          <t>Ticket sales outside EU</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>81002</t>
+          <t>9041</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Markup Hotels</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
+          <t>FX difference - positive</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
       <c r="G110" t="n">
-        <v>-38170.95</v>
+        <v>-242.4</v>
       </c>
       <c r="H110" t="n">
-        <v>845</v>
+        <v>35</v>
       </c>
     </row>
     <row r="111">
@@ -4101,29 +4109,21 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>81003</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Markup Other Products</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+          <t>Cashback accruals</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
       <c r="G111" t="n">
-        <v>-641.17</v>
+        <v>-154645.16</v>
       </c>
       <c r="H111" t="n">
-        <v>41</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="112">
@@ -4139,29 +4139,21 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>81003</t>
+          <t>80001</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Markup Other Products</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
+          <t>Turnover flights</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
       <c r="G112" t="n">
-        <v>-16989.31</v>
+        <v>-7865577.82</v>
       </c>
       <c r="H112" t="n">
-        <v>662</v>
+        <v>7354</v>
       </c>
     </row>
     <row r="113">
@@ -4177,29 +4169,21 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>80002</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>FX markup</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+          <t>Turnover Hotels</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
       <c r="G113" t="n">
-        <v>-4565.68</v>
+        <v>-301706.24</v>
       </c>
       <c r="H113" t="n">
-        <v>171</v>
+        <v>954</v>
       </c>
     </row>
     <row r="114">
@@ -4215,29 +4199,21 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>80003</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>FX markup</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
+          <t>Turnover Other Products</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
       <c r="G114" t="n">
-        <v>-12445.98</v>
+        <v>-131837.53</v>
       </c>
       <c r="H114" t="n">
-        <v>1229</v>
+        <v>695</v>
       </c>
     </row>
     <row r="115">
@@ -4253,12 +4229,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Consolidator markup</t>
+          <t>Turnover Saas montly fees</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4268,14 +4244,14 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>1E</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>-708.01</v>
+        <v>-2409</v>
       </c>
       <c r="H115" t="n">
-        <v>154</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -4291,12 +4267,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Consolidator markup</t>
+          <t>GDS incentives</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4306,14 +4282,14 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>1E</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>-8509.77</v>
+        <v>-209365.74</v>
       </c>
       <c r="H116" t="n">
-        <v>2673</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117">
@@ -4329,12 +4305,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>81001</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>GDS incentive compensation markup</t>
+          <t>Markup Flights</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4342,16 +4318,12 @@
           <t>Margin</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+      <c r="F117" t="inlineStr"/>
       <c r="G117" t="n">
-        <v>-3632.35</v>
+        <v>-30075.09</v>
       </c>
       <c r="H117" t="n">
-        <v>149</v>
+        <v>128</v>
       </c>
     </row>
     <row r="118">
@@ -4367,12 +4339,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>81001</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>GDS incentive compensation markup</t>
+          <t>Markup Flights</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4382,14 +4354,14 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>1E</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>-24295.35</v>
+        <v>-438751.84</v>
       </c>
       <c r="H118" t="n">
-        <v>2333</v>
+        <v>7070</v>
       </c>
     </row>
     <row r="119">
@@ -4405,21 +4377,25 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>81002</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Revenue from rebooking price differences</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
+          <t>Markup Hotels</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="n">
-        <v>-5163.17</v>
+        <v>-2427.64</v>
       </c>
       <c r="H119" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="120">
@@ -4435,21 +4411,29 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>81002</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Positive variance - gain</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
+          <t>Markup Hotels</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G120" t="n">
-        <v>-7834.19</v>
+        <v>-1428</v>
       </c>
       <c r="H120" t="n">
-        <v>7049</v>
+        <v>70</v>
       </c>
     </row>
     <row r="121">
@@ -4465,21 +4449,29 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>9040</t>
+          <t>81002</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>FX difference - negative</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
+          <t>Markup Hotels</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
       <c r="G121" t="n">
-        <v>4304.45</v>
+        <v>-38170.95</v>
       </c>
       <c r="H121" t="n">
-        <v>61</v>
+        <v>845</v>
       </c>
     </row>
     <row r="122">
@@ -4495,132 +4487,156 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>9041</t>
+          <t>81003</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>FX difference - positive</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
+          <t>Markup Other Products</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="n">
-        <v>-32.06</v>
+        <v>-155.28</v>
       </c>
       <c r="H122" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ticket purchases EU</t>
+          <t>Ticket Sales within EU</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>7223</t>
+          <t>81003</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Incidentals, errors, ADM penalties</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
+          <t>Markup Other Products</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G123" t="n">
-        <v>5267.19</v>
+        <v>-485.89</v>
       </c>
       <c r="H123" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ancill services NL</t>
+          <t>Ticket Sales within EU</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>81003</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VAT payable Low</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
+          <t>Markup Other Products</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
       <c r="G124" t="n">
-        <v>-6885.65</v>
+        <v>-16989.31</v>
       </c>
       <c r="H124" t="n">
-        <v>317</v>
+        <v>662</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ancill services NL</t>
+          <t>Ticket Sales within EU</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>80002</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Turnover Hotels</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr"/>
+          <t>FX markup</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="n">
-        <v>-67109.02</v>
+        <v>-17011.66</v>
       </c>
       <c r="H125" t="n">
-        <v>316</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ancill services NL</t>
+          <t>Ticket Sales within EU</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>81002</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Markup Hotels</t>
+          <t>Consolidator markup</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -4628,377 +4644,353 @@
           <t>Margin</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>1A</t>
-        </is>
-      </c>
+      <c r="F126" t="inlineStr"/>
       <c r="G126" t="n">
-        <v>-9337.98</v>
+        <v>-615.59</v>
       </c>
       <c r="H126" t="n">
-        <v>316</v>
+        <v>93</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ancill services NL</t>
+          <t>Ticket Sales within EU</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>9040</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>FX difference - negative</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
+          <t>Consolidator markup</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G127" t="n">
-        <v>-60.17</v>
+        <v>-8602.190000000001</v>
       </c>
       <c r="H127" t="n">
-        <v>1</v>
+        <v>2734</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Ancill services purchases outside EU low (9%)</t>
+          <t>Ticket Sales within EU</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Bookings cost of sale suspense</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
+          <t>GDS incentive compensation markup</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="n">
-        <v>862238.71</v>
+        <v>-3312.6</v>
       </c>
       <c r="H128" t="n">
-        <v>10</v>
+        <v>94</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Ancill services purchases outside EU low (9%)</t>
+          <t>Ticket Sales within EU</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Gillion Interest</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
+          <t>GDS incentive compensation markup</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G129" t="n">
-        <v>40473</v>
+        <v>-24615.1</v>
       </c>
       <c r="H129" t="n">
-        <v>1</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>FEU</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Flight Margin EU (0%)</t>
+          <t>Ticket Sales within EU</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Cashback accruals</t>
+          <t>Revenue from rebooking price differences</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+      <c r="F130" t="inlineStr"/>
       <c r="G130" t="n">
-        <v>-32341.7</v>
+        <v>-5163.17</v>
       </c>
       <c r="H130" t="n">
-        <v>326</v>
+        <v>32</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>FEU</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Flight Margin EU (0%)</t>
+          <t>Ticket Sales within EU</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>81001</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Markup Flights</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+          <t>Positive variance - gain</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
       <c r="G131" t="n">
-        <v>-119346.51</v>
+        <v>-7834.19</v>
       </c>
       <c r="H131" t="n">
-        <v>2031</v>
+        <v>7049</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FEU</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Flight Margin EU (0%)</t>
+          <t>Ticket Sales within EU</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>9040</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>FX markup</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+          <t>FX difference - negative</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
       <c r="G132" t="n">
-        <v>-3373.07</v>
+        <v>4304.45</v>
       </c>
       <c r="H132" t="n">
-        <v>309</v>
+        <v>61</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>FEU</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Flight Margin EU (0%)</t>
+          <t>Ticket Sales within EU</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>9041</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Consolidator markup</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+          <t>FX difference - positive</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
       <c r="G133" t="n">
-        <v>-2198.29</v>
+        <v>-32.06</v>
       </c>
       <c r="H133" t="n">
-        <v>782</v>
+        <v>20</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>FEU</t>
+          <t>91</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Flight Margin EU (0%)</t>
+          <t>Ticket purchases EU</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>7223</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>GDS incentive compensation markup</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+          <t>Incidentals, errors, ADM penalties</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
       <c r="G134" t="n">
-        <v>-5915.43</v>
+        <v>5267.19</v>
       </c>
       <c r="H134" t="n">
-        <v>652</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>FEU</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Flight Margin EU (0%)</t>
+          <t>Ancill services NL</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Revenue from rebooking price differences</t>
+          <t>VAT payable Low</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+      <c r="F135" t="inlineStr"/>
       <c r="G135" t="n">
-        <v>-108.08</v>
+        <v>-6885.65</v>
       </c>
       <c r="H135" t="n">
-        <v>4</v>
+        <v>317</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>VAT Exempt - financial services</t>
+          <t>Ancill services NL</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>80002</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Insurance costs Illness</t>
+          <t>Turnover Hotels</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="n">
-        <v>294.5</v>
+        <v>-67109.02</v>
       </c>
       <c r="H136" t="n">
-        <v>1</v>
+        <v>316</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>VAT Exempt - financial services</t>
+          <t>Ancill services NL</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>81002</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>GDS incentives</t>
+          <t>Markup Hotels</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -5008,369 +5000,405 @@
       </c>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="n">
-        <v>-9218.35</v>
+        <v>-175</v>
       </c>
       <c r="H137" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>VAT Exempt</t>
+          <t>Ancill services NL</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>81002</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Amex Credit card costs</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
+          <t>Markup Hotels</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
       <c r="G138" t="n">
-        <v>-7719.08</v>
+        <v>-9162.98</v>
       </c>
       <c r="H138" t="n">
-        <v>245</v>
+        <v>304</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>VAT Exempt - financial services</t>
+          <t>Ancill services NL</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>9040</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Amex Credit card costs</t>
+          <t>FX difference - negative</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="n">
-        <v>-276.1</v>
+        <v>-60.17</v>
       </c>
       <c r="H139" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>97</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>VAT Exempt</t>
+          <t>Ancill services purchases outside EU low (9%)</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Ecommpay fee EUR</t>
+          <t>Bookings cost of sale suspense</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="n">
-        <v>-1110.56</v>
+        <v>862238.71</v>
       </c>
       <c r="H140" t="n">
-        <v>169</v>
+        <v>10</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>97</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>VAT Exempt - financial services</t>
+          <t>Ancill services purchases outside EU low (9%)</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>9029</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Ecommpay fee EUR</t>
+          <t>Gillion Interest</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="n">
-        <v>-48.51</v>
+        <v>40473</v>
       </c>
       <c r="H141" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>FEU</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>VAT Exempt</t>
+          <t>Flight Margin EU (0%)</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>8113</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Ecommpay fee USD</t>
+          <t>Cashback accruals</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G142" t="n">
-        <v>-34.01</v>
+        <v>-32341.7</v>
       </c>
       <c r="H142" t="n">
-        <v>2</v>
+        <v>326</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>FEU</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>VAT Exempt</t>
+          <t>Flight Margin EU (0%)</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>81001</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Payment method fees ancillary services NL Corporate</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
+          <t>Markup Flights</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G143" t="n">
-        <v>-291.82</v>
+        <v>-119346.51</v>
       </c>
       <c r="H143" t="n">
-        <v>49</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>FEU</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>VAT Exempt - financial services</t>
+          <t>Flight Margin EU (0%)</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Payment method fees ancillary services NL Corporate</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr"/>
+          <t>FX markup</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="n">
-        <v>-2.97</v>
+        <v>-3373.07</v>
       </c>
       <c r="H144" t="n">
-        <v>1</v>
+        <v>309</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>FWW</t>
+          <t>FEU</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Flight Margin Non-EU</t>
+          <t>Flight Margin EU (0%)</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Cashback accruals</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
+          <t>Consolidator markup</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G145" t="n">
-        <v>-5491.87</v>
+        <v>-2198.29</v>
       </c>
       <c r="H145" t="n">
-        <v>93</v>
+        <v>782</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>FWW</t>
+          <t>FEU</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Flight Margin Non-EU</t>
+          <t>Flight Margin EU (0%)</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>80001</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Turnover flights</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
+          <t>GDS incentive compensation markup</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G146" t="n">
-        <v>-1319018.6</v>
+        <v>-5915.43</v>
       </c>
       <c r="H146" t="n">
-        <v>1149</v>
+        <v>652</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>FWW</t>
+          <t>FEU</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Flight Margin Non-EU</t>
+          <t>Flight Margin EU (0%)</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>81001</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Markup Flights</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr"/>
+          <t>Revenue from rebooking price differences</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G147" t="n">
-        <v>-66693.53</v>
+        <v>-108.08</v>
       </c>
       <c r="H147" t="n">
-        <v>1148</v>
+        <v>4</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>FWW</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Flight Margin Non-EU</t>
+          <t>VAT Exempt - financial services</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>FX markup</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
+          <t>Insurance costs Illness</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="n">
-        <v>-5477.37</v>
+        <v>294.5</v>
       </c>
       <c r="H148" t="n">
-        <v>842</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>FWW</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Flight Margin Non-EU</t>
+          <t>VAT Exempt - financial services</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Consolidator markup</t>
+          <t>GDS incentives</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5378,263 +5406,223 @@
           <t>Margin</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G149" t="n">
-        <v>-1013.38</v>
+        <v>-9218.35</v>
       </c>
       <c r="H149" t="n">
-        <v>475</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>FWW</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Flight Margin Non-EU</t>
+          <t>VAT Exempt</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>GDS incentive compensation markup</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
+          <t>Amex Credit card costs</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="n">
-        <v>-3062.05</v>
+        <v>-7719.08</v>
       </c>
       <c r="H150" t="n">
-        <v>400</v>
+        <v>245</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>FWW</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Flight Margin Non-EU</t>
+          <t>VAT Exempt - financial services</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Revenue from rebooking price differences</t>
+          <t>Amex Credit card costs</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="n">
-        <v>205.61</v>
+        <v>-276.1</v>
       </c>
       <c r="H151" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>NEU</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>EU Sales Reverse Charge</t>
+          <t>VAT Exempt</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>GDS incentives</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
+          <t>Ecommpay fee EUR</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
       <c r="G152" t="n">
-        <v>-18917.58</v>
+        <v>-1110.56</v>
       </c>
       <c r="H152" t="n">
-        <v>1</v>
+        <v>169</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>NEU</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>EU Sales Reverse Charge</t>
+          <t>VAT Exempt - financial services</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>8090</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Platform subscription fee</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
+          <t>Ecommpay fee EUR</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
       <c r="G153" t="n">
-        <v>-500</v>
+        <v>-48.51</v>
       </c>
       <c r="H153" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>NEU</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>EU Sales Reverse Charge</t>
+          <t>VAT Exempt</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>8091</t>
+          <t>8113</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Minimum booking fee</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
+          <t>Ecommpay fee USD</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
       <c r="G154" t="n">
-        <v>-117.69</v>
+        <v>-34.01</v>
       </c>
       <c r="H154" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>NEU</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>EU Sales Reverse Charge</t>
+          <t>VAT Exempt</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>81003</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Markup Other Products</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
+          <t>Payment method fees ancillary services NL Corporate</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
       <c r="G155" t="n">
-        <v>-25</v>
+        <v>-291.82</v>
       </c>
       <c r="H155" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>NEX</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Non Flight Margin 0%</t>
+          <t>VAT Exempt - financial services</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>8090</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Platform subscription fee</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+          <t>Payment method fees ancillary services NL Corporate</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
       <c r="G156" t="n">
-        <v>-250</v>
+        <v>-2.97</v>
       </c>
       <c r="H156" t="n">
         <v>1</v>
@@ -5643,94 +5631,82 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>NEX</t>
+          <t>FWW</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Non Flight Margin 0%</t>
+          <t>Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>81003</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Markup Other Products</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+          <t>Cashback accruals</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
       <c r="G157" t="n">
-        <v>-50</v>
+        <v>-5491.87</v>
       </c>
       <c r="H157" t="n">
-        <v>2</v>
+        <v>93</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>NNL</t>
+          <t>FWW</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Domestic Sales High (21%)</t>
+          <t>Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>80001</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VAT payable High</t>
+          <t>Turnover flights</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>1A</t>
-        </is>
-      </c>
+      <c r="F158" t="inlineStr"/>
       <c r="G158" t="n">
-        <v>-26.25</v>
+        <v>-1319018.6</v>
       </c>
       <c r="H158" t="n">
-        <v>2</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>NNL</t>
+          <t>FWW</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Domestic Sales High (21%)</t>
+          <t>Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>81003</t>
+          <t>81001</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Markup Other Products</t>
+          <t>Markup Flights</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -5738,97 +5714,101 @@
           <t>Margin</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>1A</t>
-        </is>
-      </c>
+      <c r="F159" t="inlineStr"/>
       <c r="G159" t="n">
-        <v>-125</v>
+        <v>-66693.53</v>
       </c>
       <c r="H159" t="n">
-        <v>2</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>NWW</t>
+          <t>FWW</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Non-Flight Margin Non-EU</t>
+          <t>Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>80002</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Turnover Hotels</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr"/>
+          <t>FX markup</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="n">
-        <v>-46083.51</v>
+        <v>-5477.37</v>
       </c>
       <c r="H160" t="n">
-        <v>134</v>
+        <v>842</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>NWW</t>
+          <t>FWW</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Non-Flight Margin Non-EU</t>
+          <t>Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>80003</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Turnover Other Products</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr"/>
+          <t>Consolidator markup</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="n">
-        <v>-881.5</v>
+        <v>-1013.38</v>
       </c>
       <c r="H161" t="n">
-        <v>2</v>
+        <v>475</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>NWW</t>
+          <t>FWW</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Non-Flight Margin Non-EU</t>
+          <t>Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>8091</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Minimum booking fee</t>
+          <t>GDS incentive compensation markup</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -5838,65 +5818,61 @@
       </c>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="n">
-        <v>-2249.36</v>
+        <v>-3062.05</v>
       </c>
       <c r="H162" t="n">
-        <v>22</v>
+        <v>400</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>NWW</t>
+          <t>FWW</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Non-Flight Margin Non-EU</t>
+          <t>Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>81002</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Markup Hotels</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
+          <t>Revenue from rebooking price differences</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="n">
-        <v>-1.15</v>
+        <v>205.61</v>
       </c>
       <c r="H163" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>NWW</t>
+          <t>NEU</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Non-Flight Margin Non-EU</t>
+          <t>EU Sales Reverse Charge</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>81003</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Markup Other Products</t>
+          <t>GDS incentives</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -5904,153 +5880,189 @@
           <t>Margin</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G164" t="n">
-        <v>-91.23999999999999</v>
+        <v>-18917.58</v>
       </c>
       <c r="H164" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>NWW</t>
+          <t>NEU</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Non-Flight Margin Non-EU</t>
+          <t>EU Sales Reverse Charge</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>8090</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Amex Credit card costs</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
+          <t>Platform subscription fee</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
       <c r="G165" t="n">
-        <v>-4157.92</v>
+        <v>-500</v>
       </c>
       <c r="H165" t="n">
-        <v>167</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>NWW</t>
+          <t>NEU</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Non-Flight Margin Non-EU</t>
+          <t>EU Sales Reverse Charge</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8091</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Ecommpay fee EUR</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
+          <t>Minimum booking fee</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
       <c r="G166" t="n">
-        <v>-1873.3</v>
+        <v>-117.69</v>
       </c>
       <c r="H166" t="n">
-        <v>146</v>
+        <v>9</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>NWW</t>
+          <t>NEU</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Non-Flight Margin Non-EU</t>
+          <t>EU Sales Reverse Charge</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>8113</t>
+          <t>81003</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Ecommpay fee USD</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
+          <t>Markup Other Products</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
       <c r="G167" t="n">
-        <v>-3748.14</v>
+        <v>-25</v>
       </c>
       <c r="H167" t="n">
-        <v>126</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>NWW</t>
+          <t>NEX</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Non-Flight Margin Non-EU</t>
+          <t>Non Flight Margin 0%</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>8114</t>
+          <t>8090</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Ecommpay fee GBP</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
+          <t>Platform subscription fee</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G168" t="n">
-        <v>-787.22</v>
+        <v>-250</v>
       </c>
       <c r="H168" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>NWW</t>
+          <t>NEX</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Non-Flight Margin Non-EU</t>
+          <t>Non Flight Margin 0%</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>82002</t>
+          <t>81003</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Commission Hotels</t>
+          <t>Markup Other Products</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -6058,83 +6070,99 @@
           <t>Margin</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G169" t="n">
-        <v>-6591.13</v>
+        <v>-50</v>
       </c>
       <c r="H169" t="n">
-        <v>133</v>
+        <v>2</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>NWW</t>
+          <t>NNL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Non-Flight Margin Non-EU</t>
+          <t>Domestic Sales High (21%)</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Payment method fees ancillary services NL Corporate</t>
+          <t>VAT payable High</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
       <c r="G170" t="n">
-        <v>-679.77</v>
+        <v>-26.25</v>
       </c>
       <c r="H170" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>PAS</t>
+          <t>NNL</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Paid on behalf of customer</t>
+          <t>Domestic Sales High (21%)</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>80001</t>
+          <t>81003</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Turnover flights</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
+          <t>Markup Other Products</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
       <c r="G171" t="n">
-        <v>-2106220.81</v>
+        <v>-125</v>
       </c>
       <c r="H171" t="n">
-        <v>2047</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>PAS</t>
+          <t>NWW</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Paid on behalf of customer</t>
+          <t>Non-Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6150,21 +6178,21 @@
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="n">
-        <v>-80905.00999999999</v>
+        <v>-46083.51</v>
       </c>
       <c r="H172" t="n">
-        <v>256</v>
+        <v>134</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>PAS</t>
+          <t>NWW</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Paid on behalf of customer</t>
+          <t>Non-Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6180,31 +6208,31 @@
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="n">
-        <v>-1286.28</v>
+        <v>-881.5</v>
       </c>
       <c r="H173" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>PAS</t>
+          <t>NWW</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Paid on behalf of customer</t>
+          <t>Non-Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>82002</t>
+          <t>8091</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Commission Hotels</t>
+          <t>Minimum booking fee</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -6214,31 +6242,31 @@
       </c>
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="n">
-        <v>-498.39</v>
+        <v>-2249.36</v>
       </c>
       <c r="H174" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PAS</t>
+          <t>NWW</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Paid on behalf of customer</t>
+          <t>Non-Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>82002</t>
+          <t>81002</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Commission Hotels</t>
+          <t>Markup Hotels</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -6246,37 +6274,33 @@
           <t>Margin</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>1A</t>
-        </is>
-      </c>
+      <c r="F175" t="inlineStr"/>
       <c r="G175" t="n">
-        <v>-2304</v>
+        <v>-1.15</v>
       </c>
       <c r="H175" t="n">
-        <v>77</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>PAS</t>
+          <t>NWW</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Paid on behalf of customer</t>
+          <t>Non-Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>82002</t>
+          <t>81003</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Commission Hotels</t>
+          <t>Markup Other Products</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -6284,315 +6308,283 @@
           <t>Margin</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+      <c r="F176" t="inlineStr"/>
       <c r="G176" t="n">
-        <v>-298</v>
+        <v>-91.23999999999999</v>
       </c>
       <c r="H176" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>PAS</t>
+          <t>NWW</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Paid on behalf of customer</t>
+          <t>Non-Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>82002</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Commission Hotels</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
+          <t>Amex Credit card costs</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
       <c r="G177" t="n">
-        <v>-8206.57</v>
+        <v>-4157.92</v>
       </c>
       <c r="H177" t="n">
-        <v>150</v>
+        <v>167</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>UEU</t>
+          <t>NWW</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>European Reverse Charge</t>
+          <t>Non-Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>40751</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Outsourced personnel - IT Team</t>
+          <t>Ecommpay fee EUR</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>4B, 5B</t>
-        </is>
-      </c>
+      <c r="F178" t="inlineStr"/>
       <c r="G178" t="n">
-        <v>5150</v>
+        <v>-1873.3</v>
       </c>
       <c r="H178" t="n">
-        <v>1</v>
+        <v>146</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>UEU</t>
+          <t>NWW</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>European Reverse Charge</t>
+          <t>Non-Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>40755</t>
+          <t>8113</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Outsourced personnel - Product Team</t>
+          <t>Ecommpay fee USD</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>4B, 5B</t>
-        </is>
-      </c>
+      <c r="F179" t="inlineStr"/>
       <c r="G179" t="n">
-        <v>4200</v>
+        <v>-3748.14</v>
       </c>
       <c r="H179" t="n">
-        <v>1</v>
+        <v>126</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>UN9</t>
+          <t>NWW</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Domestic Purchases Low (9%)</t>
+          <t>Non-Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Vat Receivable (low)</t>
+          <t>Ecommpay fee GBP</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="n">
-        <v>222.35</v>
+        <v>-787.22</v>
       </c>
       <c r="H180" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>UN9</t>
+          <t>NWW</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Domestic Purchases Low (9%)</t>
+          <t>Non-Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>82002</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Other Personnel Costs</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>5B</t>
-        </is>
-      </c>
+          <t>Commission Hotels</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr"/>
       <c r="G181" t="n">
-        <v>2470.62</v>
+        <v>-6591.13</v>
       </c>
       <c r="H181" t="n">
-        <v>2</v>
+        <v>133</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>UNL</t>
+          <t>NWW</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Domestic Purchases High (21%)</t>
+          <t>Non-Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Vat Receivable (high)</t>
+          <t>Payment method fees ancillary services NL Corporate</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="n">
-        <v>423.5</v>
+        <v>-679.77</v>
       </c>
       <c r="H182" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>UNL</t>
+          <t>PAS</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Domestic Purchases High (21%)</t>
+          <t>Paid on behalf of customer</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>80001</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Other Personnel Costs</t>
+          <t>Turnover flights</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>5B</t>
-        </is>
-      </c>
+      <c r="F183" t="inlineStr"/>
       <c r="G183" t="n">
-        <v>2016.67</v>
+        <v>-2106220.81</v>
       </c>
       <c r="H183" t="n">
-        <v>1</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>UWW</t>
+          <t>PAS</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Non-EU Purchases Reverse Charge</t>
+          <t>Paid on behalf of customer</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>80002</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Cashback accruals</t>
+          <t>Turnover Hotels</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>4A, 5B</t>
-        </is>
-      </c>
+      <c r="F184" t="inlineStr"/>
       <c r="G184" t="n">
-        <v>14490</v>
+        <v>-80905.00999999999</v>
       </c>
       <c r="H184" t="n">
-        <v>2</v>
+        <v>256</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>UWW</t>
+          <t>PAS</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Non-EU Purchases Reverse Charge</t>
+          <t>Paid on behalf of customer</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>40751</t>
+          <t>80003</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Outsourced personnel - IT Team</t>
+          <t>Turnover Other Products</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>4A, 5B</t>
-        </is>
-      </c>
+      <c r="F185" t="inlineStr"/>
       <c r="G185" t="n">
-        <v>31075</v>
+        <v>-1286.28</v>
       </c>
       <c r="H185" t="n">
         <v>6</v>
@@ -6601,204 +6593,616 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>UWW</t>
+          <t>PAS</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Non-EU Purchases Reverse Charge</t>
+          <t>Paid on behalf of customer</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>40752</t>
+          <t>82002</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Outsourced personnel - Finance Team</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>4A, 5B</t>
-        </is>
-      </c>
+          <t>Commission Hotels</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr"/>
       <c r="G186" t="n">
-        <v>1750</v>
+        <v>-498.39</v>
       </c>
       <c r="H186" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>UWW</t>
+          <t>PAS</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Non-EU Purchases Reverse Charge</t>
+          <t>Paid on behalf of customer</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>40754</t>
+          <t>82002</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Outsourced personnel - Operations Team</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr"/>
+          <t>Commission Hotels</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>4A, 5B</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="G187" t="n">
-        <v>6451.69</v>
+        <v>-2304</v>
       </c>
       <c r="H187" t="n">
-        <v>4</v>
+        <v>77</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>UWW</t>
+          <t>PAS</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Non-EU Purchases Reverse Charge</t>
+          <t>Paid on behalf of customer</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>40755</t>
+          <t>82002</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Outsourced personnel - Product Team</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr"/>
+          <t>Commission Hotels</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>4A, 5B</t>
+          <t>1E</t>
         </is>
       </c>
       <c r="G188" t="n">
-        <v>10400</v>
+        <v>-298</v>
       </c>
       <c r="H188" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>UWW</t>
+          <t>PAS</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Non-EU Purchases Reverse Charge</t>
+          <t>Paid on behalf of customer</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>40757</t>
+          <t>82002</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Outsourced personnel - Customer Success Team</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr"/>
+          <t>Commission Hotels</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>4A, 5B</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="G189" t="n">
-        <v>3855</v>
+        <v>-8206.57</v>
       </c>
       <c r="H189" t="n">
-        <v>2</v>
+        <v>150</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>UWW</t>
+          <t>UEU</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Non-EU Purchases Reverse Charge</t>
+          <t>European Reverse Charge</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>40751</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Conferences and exhibitions</t>
+          <t>Outsourced personnel - IT Team</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
-          <t>4A, 5B</t>
+          <t>4B, 5B</t>
         </is>
       </c>
       <c r="G190" t="n">
-        <v>12877.03</v>
+        <v>5150</v>
       </c>
       <c r="H190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>UWW</t>
+          <t>UEU</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Non-EU Purchases Reverse Charge</t>
+          <t>European Reverse Charge</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>40755</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Advisory costs</t>
+          <t>Outsourced personnel - Product Team</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
+          <t>4B, 5B</t>
+        </is>
+      </c>
+      <c r="G191" t="n">
+        <v>4200</v>
+      </c>
+      <c r="H191" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>UN9</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Domestic Purchases Low (9%)</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Vat Receivable (low)</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="n">
+        <v>222.35</v>
+      </c>
+      <c r="H192" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>UN9</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Domestic Purchases Low (9%)</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>4074</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Other Personnel Costs</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>5B</t>
+        </is>
+      </c>
+      <c r="G193" t="n">
+        <v>2470.62</v>
+      </c>
+      <c r="H193" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>UNL</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Domestic Purchases High (21%)</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>1511</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Vat Receivable (high)</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="n">
+        <v>423.5</v>
+      </c>
+      <c r="H194" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>UNL</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Domestic Purchases High (21%)</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>4074</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Other Personnel Costs</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>5B</t>
+        </is>
+      </c>
+      <c r="G195" t="n">
+        <v>2016.67</v>
+      </c>
+      <c r="H195" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>UWW</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Non-EU Purchases Reverse Charge</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>1602</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Cashback accruals</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr">
+        <is>
           <t>4A, 5B</t>
         </is>
       </c>
-      <c r="G191" t="n">
+      <c r="G196" t="n">
+        <v>14490</v>
+      </c>
+      <c r="H196" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>UWW</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Non-EU Purchases Reverse Charge</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>40751</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Outsourced personnel - IT Team</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>4A, 5B</t>
+        </is>
+      </c>
+      <c r="G197" t="n">
+        <v>31075</v>
+      </c>
+      <c r="H197" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>UWW</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Non-EU Purchases Reverse Charge</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>40752</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Outsourced personnel - Finance Team</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>4A, 5B</t>
+        </is>
+      </c>
+      <c r="G198" t="n">
+        <v>1750</v>
+      </c>
+      <c r="H198" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>UWW</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Non-EU Purchases Reverse Charge</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>40754</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Outsourced personnel - Operations Team</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>4A, 5B</t>
+        </is>
+      </c>
+      <c r="G199" t="n">
+        <v>6451.69</v>
+      </c>
+      <c r="H199" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>UWW</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Non-EU Purchases Reverse Charge</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>40755</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Outsourced personnel - Product Team</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>4A, 5B</t>
+        </is>
+      </c>
+      <c r="G200" t="n">
+        <v>10400</v>
+      </c>
+      <c r="H200" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>UWW</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Non-EU Purchases Reverse Charge</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>40757</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Outsourced personnel - Customer Success Team</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>4A, 5B</t>
+        </is>
+      </c>
+      <c r="G201" t="n">
+        <v>3855</v>
+      </c>
+      <c r="H201" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>UWW</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Non-EU Purchases Reverse Charge</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>4340</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Conferences and exhibitions</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>4A, 5B</t>
+        </is>
+      </c>
+      <c r="G202" t="n">
+        <v>12877.03</v>
+      </c>
+      <c r="H202" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>UWW</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Non-EU Purchases Reverse Charge</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>4856</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Advisory costs</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>4A, 5B</t>
+        </is>
+      </c>
+      <c r="G203" t="n">
         <v>6571.35</v>
       </c>
-      <c r="H191" t="n">
+      <c r="H203" t="n">
         <v>1</v>
       </c>
     </row>

--- a/output/VAT transaction lines Q2'26.xlsx
+++ b/output/VAT transaction lines Q2'26.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H203"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1404,10 +1404,10 @@
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>-6090.68</v>
+        <v>-6148.71</v>
       </c>
       <c r="H29" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30">
@@ -1423,29 +1423,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>8091</t>
+          <t>9040</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Minimum booking fee</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
+          <t>FX difference - negative</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
-        <v>-58.03</v>
+        <v>13.03</v>
       </c>
       <c r="H30" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31">
@@ -1461,51 +1453,51 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>9040</t>
+          <t>9041</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FX difference - negative</t>
+          <t>FX difference - positive</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>13.03</v>
+        <v>15.75</v>
       </c>
       <c r="H31" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Commission Non EU</t>
+          <t>Purchases outside EU</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>9041</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FX difference - positive</t>
+          <t>Deposits to suppliers</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>15.75</v>
+        <v>27500</v>
       </c>
       <c r="H32" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -1521,21 +1513,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Deposits to suppliers</t>
+          <t>Vat Receivable (high)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>27500</v>
+        <v>84279.99000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34">
@@ -1551,18 +1543,18 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Vat Receivable (high)</t>
+          <t>Purchases outside EU</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>84279.99000000001</v>
+        <v>-84279.99000000001</v>
       </c>
       <c r="H34" t="n">
         <v>83</v>
@@ -1581,21 +1573,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Purchases outside EU</t>
+          <t>Cashback accruals</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>-84279.99000000001</v>
+        <v>25867.98</v>
       </c>
       <c r="H35" t="n">
-        <v>83</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1611,21 +1603,25 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>40751</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cashback accruals</t>
+          <t>Outsourced personnel - IT Team</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>4A, 5B</t>
+        </is>
+      </c>
       <c r="G36" t="n">
-        <v>25867.98</v>
+        <v>184781.67</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37">
@@ -1641,12 +1637,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>40751</t>
+          <t>40754</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Outsourced personnel - IT Team</t>
+          <t>Outsourced personnel - Operations Team</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1656,10 +1652,10 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>184781.67</v>
+        <v>33615.89</v>
       </c>
       <c r="H37" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38">
@@ -1675,12 +1671,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>40754</t>
+          <t>40755</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Outsourced personnel - Operations Team</t>
+          <t>Outsourced personnel - Product Team</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -1690,10 +1686,10 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>33615.89</v>
+        <v>9600</v>
       </c>
       <c r="H38" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -1709,12 +1705,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>40755</t>
+          <t>40756</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Outsourced personnel - Product Team</t>
+          <t>Outsourced personnel - Sales Team</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1724,7 +1720,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>9600</v>
+        <v>15000</v>
       </c>
       <c r="H39" t="n">
         <v>3</v>
@@ -1743,12 +1739,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>40756</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Outsourced personnel - Sales Team</t>
+          <t>Conferences and exhibitions</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -1758,10 +1754,10 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>15000</v>
+        <v>2073.29</v>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -1777,12 +1773,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Conferences and exhibitions</t>
+          <t>Subscriptions product team</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1792,10 +1788,10 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>2073.29</v>
+        <v>1807.84</v>
       </c>
       <c r="H41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1811,12 +1807,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>4821</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Subscriptions product team</t>
+          <t>Subscriptions Sales</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1826,7 +1822,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1807.84</v>
+        <v>686.05</v>
       </c>
       <c r="H42" t="n">
         <v>1</v>
@@ -1845,12 +1841,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>4825</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Subscriptions Sales</t>
+          <t>Digital Marketing expenses</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1860,7 +1856,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>686.05</v>
+        <v>229.8</v>
       </c>
       <c r="H43" t="n">
         <v>1</v>
@@ -1879,12 +1875,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Digital Marketing expenses</t>
+          <t>Subscriptions Operations</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -1894,7 +1890,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>229.8</v>
+        <v>3958.5</v>
       </c>
       <c r="H44" t="n">
         <v>1</v>
@@ -1913,12 +1909,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>7223</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Subscriptions Operations</t>
+          <t>Incidentals, errors, ADM penalties</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -1928,7 +1924,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>3958.5</v>
+        <v>255.86</v>
       </c>
       <c r="H45" t="n">
         <v>1</v>
@@ -1947,22 +1943,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>7223</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Incidentals, errors, ADM penalties</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>4A, 5B</t>
-        </is>
-      </c>
+          <t>Turnover Saas montly fees</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
-        <v>255.86</v>
+        <v>-17.26</v>
       </c>
       <c r="H46" t="n">
         <v>1</v>
@@ -1981,55 +1977,51 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>9040</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Turnover Saas montly fees</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
+          <t>FX difference - negative</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
-        <v>-17.26</v>
+        <v>159.3</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Purchases outside EU</t>
+          <t>Sales Margin 21% NL</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>9040</t>
+          <t>80003</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>FX difference - negative</t>
+          <t>Turnover Other Products</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
-        <v>159.3</v>
+        <v>-1046.59</v>
       </c>
       <c r="H48" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -2045,18 +2037,26 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>80003</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Turnover Other Products</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
+          <t>Turnover Saas montly fees</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
       <c r="G49" t="n">
-        <v>-1046.59</v>
+        <v>-7332.21</v>
       </c>
       <c r="H49" t="n">
         <v>3</v>
@@ -2075,12 +2075,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>81003</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Turnover Saas montly fees</t>
+          <t>Markup Other Products</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>-7332.21</v>
+        <v>-75</v>
       </c>
       <c r="H50" t="n">
         <v>3</v>
@@ -2103,39 +2103,31 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Sales Margin 21% NL</t>
+          <t>Ticket sales NL 0%</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>81003</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Markup Other Products</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>1A</t>
-        </is>
-      </c>
+          <t>Bookings cost of sale suspense</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
-        <v>-75</v>
+        <v>3285155.61</v>
       </c>
       <c r="H51" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
     </row>
     <row r="52">
@@ -2151,21 +2143,21 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Bookings cost of sale suspense</t>
+          <t>Unexpected cost to be reconciled</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
-        <v>3285155.61</v>
+        <v>240.51</v>
       </c>
       <c r="H52" t="n">
-        <v>55</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53">
@@ -2181,21 +2173,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Unexpected cost to be reconciled</t>
+          <t>Cashback accruals</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
-        <v>240.51</v>
+        <v>-25320</v>
       </c>
       <c r="H53" t="n">
-        <v>15</v>
+        <v>607</v>
       </c>
     </row>
     <row r="54">
@@ -2211,21 +2203,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Cashback accruals</t>
+          <t>Suspense - research payments manually</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
-        <v>-25320</v>
+        <v>2749890.76</v>
       </c>
       <c r="H54" t="n">
-        <v>607</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -2241,21 +2233,29 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Suspense - research payments manually</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
+          <t>Consolidator fees costs</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G55" t="n">
-        <v>2749890.76</v>
+        <v>20903.57</v>
       </c>
       <c r="H55" t="n">
-        <v>3</v>
+        <v>9648</v>
       </c>
     </row>
     <row r="56">
@@ -2271,25 +2271,21 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>80001</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Consolidator fees costs</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
+          <t>Turnover flights</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
-        <v>20903.57</v>
+        <v>-4476797.29</v>
       </c>
       <c r="H56" t="n">
-        <v>9648</v>
+        <v>3659</v>
       </c>
     </row>
     <row r="57">
@@ -2305,21 +2301,21 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>80001</t>
+          <t>80003</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Turnover flights</t>
+          <t>Turnover Other Products</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
-        <v>-4476797.29</v>
+        <v>-35270.21</v>
       </c>
       <c r="H57" t="n">
-        <v>3659</v>
+        <v>220</v>
       </c>
     </row>
     <row r="58">
@@ -2335,21 +2331,29 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>80003</t>
+          <t>81001</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Turnover Other Products</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
+          <t>Markup Flights</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G58" t="n">
-        <v>-35270.21</v>
+        <v>-196950.74</v>
       </c>
       <c r="H58" t="n">
-        <v>220</v>
+        <v>3575</v>
       </c>
     </row>
     <row r="59">
@@ -2365,12 +2369,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>81001</t>
+          <t>81003</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Markup Flights</t>
+          <t>Markup Other Products</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2378,12 +2382,16 @@
           <t>Margin</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G59" t="n">
-        <v>-6083</v>
+        <v>-3297.74</v>
       </c>
       <c r="H59" t="n">
-        <v>155</v>
+        <v>216</v>
       </c>
     </row>
     <row r="60">
@@ -2399,12 +2407,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>81001</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Markup Flights</t>
+          <t>FX markup</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2418,10 +2426,10 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>-190867.74</v>
+        <v>-7945.92</v>
       </c>
       <c r="H60" t="n">
-        <v>3420</v>
+        <v>602</v>
       </c>
     </row>
     <row r="61">
@@ -2437,12 +2445,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>81003</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Markup Other Products</t>
+          <t>Consolidator markup</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2450,12 +2458,16 @@
           <t>Margin</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G61" t="n">
-        <v>-308.32</v>
+        <v>-2843.07</v>
       </c>
       <c r="H61" t="n">
-        <v>19</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="62">
@@ -2471,12 +2483,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>81003</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Markup Other Products</t>
+          <t>GDS incentive compensation markup</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2486,14 +2498,14 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1A</t>
+          <t>1E</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>-2989.42</v>
+        <v>-8804.530000000001</v>
       </c>
       <c r="H62" t="n">
-        <v>197</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="63">
@@ -2509,25 +2521,21 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>FX markup</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
+          <t>Revenue from rebooking price differences</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>-7945.92</v>
+        <v>-653.14</v>
       </c>
       <c r="H63" t="n">
-        <v>602</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -2543,25 +2551,21 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Consolidator markup</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
+          <t>Positive variance - gain</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
-        <v>-75.84999999999999</v>
+        <v>-2272.46</v>
       </c>
       <c r="H64" t="n">
-        <v>63</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="65">
@@ -2577,191 +2581,187 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>9060</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Consolidator markup</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+          <t>Rounding differences</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
-        <v>-2767.22</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>1382</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ticket sales NL 0%</t>
+          <t>NL VAT 21% - VAT high rate, excluding (purchase)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>GDS incentive compensation markup</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
+          <t>Vat Receivable (high)</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
-        <v>-155.74</v>
+        <v>20339.86</v>
       </c>
       <c r="H66" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ticket sales NL 0%</t>
+          <t>NL VAT 21% - VAT high rate, excluding (purchase)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>GDS incentive compensation markup</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
+          <t>Management Fee</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1E</t>
+          <t>5B</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>-8648.790000000001</v>
+        <v>32766</v>
       </c>
       <c r="H67" t="n">
-        <v>1211</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ticket sales NL 0%</t>
+          <t>NL VAT 21% - VAT high rate, excluding (purchase)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Revenue from rebooking price differences</t>
+          <t>Insurance costs Illness</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>5B</t>
+        </is>
+      </c>
       <c r="G68" t="n">
-        <v>-653.14</v>
+        <v>425.33</v>
       </c>
       <c r="H68" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ticket sales NL 0%</t>
+          <t>NL VAT 21% - VAT high rate, excluding (purchase)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Positive variance - gain</t>
+          <t>Other Personnel Costs</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>5B</t>
+        </is>
+      </c>
       <c r="G69" t="n">
-        <v>-2272.46</v>
+        <v>3344.18</v>
       </c>
       <c r="H69" t="n">
-        <v>2362</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ticket sales NL 0%</t>
+          <t>NL VAT 21% - VAT high rate, excluding (purchase)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>9060</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Rounding differences</t>
+          <t>Recruitment fees</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>5B</t>
+        </is>
+      </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>194.02</v>
       </c>
       <c r="H70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -2777,21 +2777,25 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Vat Receivable (high)</t>
+          <t>Office rent</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>5B</t>
+        </is>
+      </c>
       <c r="G71" t="n">
-        <v>20339.86</v>
+        <v>32963.76</v>
       </c>
       <c r="H71" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -2807,12 +2811,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>4140</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Management Fee</t>
+          <t>Cleaning Fee</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -2822,7 +2826,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>32766</v>
+        <v>1110.27</v>
       </c>
       <c r="H72" t="n">
         <v>3</v>
@@ -2841,12 +2845,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Insurance costs Illness</t>
+          <t>Conferences and exhibitions</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -2856,10 +2860,10 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>425.33</v>
+        <v>20421.49</v>
       </c>
       <c r="H73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -2875,25 +2879,21 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Other Personnel Costs</t>
+          <t>Legal costs</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>5B</t>
-        </is>
-      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
-        <v>3344.18</v>
+        <v>-2608.95</v>
       </c>
       <c r="H74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -2909,12 +2909,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Recruitment fees</t>
+          <t>Legal costs</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -2924,10 +2924,10 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>194.02</v>
+        <v>7987.11</v>
       </c>
       <c r="H75" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
@@ -2943,12 +2943,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>48204</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Office rent</t>
+          <t>IT Data feeds</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -2958,10 +2958,10 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>32963.76</v>
+        <v>2110</v>
       </c>
       <c r="H76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>4823</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Cleaning Fee</t>
+          <t>Subscriptions finance</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -2992,10 +2992,10 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>1110.27</v>
+        <v>2904</v>
       </c>
       <c r="H77" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78">
@@ -3011,12 +3011,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Conferences and exhibitions</t>
+          <t>Digital Marketing expenses</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -3026,10 +3026,10 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>20421.49</v>
+        <v>202.59</v>
       </c>
       <c r="H78" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -3045,21 +3045,25 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>4510</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Legal costs</t>
+          <t>Subscriptions General</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>5B</t>
+        </is>
+      </c>
       <c r="G79" t="n">
-        <v>-2608.95</v>
+        <v>2970</v>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -3075,12 +3079,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>4510</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Legal costs</t>
+          <t>Telephone and fax costs</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -3090,10 +3094,10 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>7987.11</v>
+        <v>132.68</v>
       </c>
       <c r="H80" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -3109,12 +3113,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>48204</t>
+          <t>4853</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>IT Data feeds</t>
+          <t>Administration costs Acountant</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -3124,10 +3128,10 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>2110</v>
+        <v>1306.25</v>
       </c>
       <c r="H81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -3143,25 +3147,21 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>4856</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Subscriptions finance</t>
+          <t>Advisory costs</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>5B</t>
-        </is>
-      </c>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
-        <v>2904</v>
+        <v>-12000</v>
       </c>
       <c r="H82" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>4856</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Digital Marketing expenses</t>
+          <t>Advisory costs</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>202.59</v>
+        <v>2407.5</v>
       </c>
       <c r="H83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -3211,25 +3211,21 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>4875</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Subscriptions General</t>
+          <t>Various office expense</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>5B</t>
-        </is>
-      </c>
+      <c r="F84" t="inlineStr"/>
       <c r="G84" t="n">
-        <v>2970</v>
+        <v>-82.56</v>
       </c>
       <c r="H84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -3245,12 +3241,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>4875</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Telephone and fax costs</t>
+          <t>Various office expense</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -3260,172 +3256,164 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>132.68</v>
+        <v>302.68</v>
       </c>
       <c r="H85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>NL VAT 21% - VAT high rate, excluding (purchase)</t>
+          <t>Ticket sales outside EU</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>4853</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Administration costs Acountant</t>
+          <t>Cashback accruals</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>5B</t>
-        </is>
-      </c>
+      <c r="F86" t="inlineStr"/>
       <c r="G86" t="n">
-        <v>1306.25</v>
+        <v>-26775.54</v>
       </c>
       <c r="H86" t="n">
-        <v>3</v>
+        <v>556</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>NL VAT 21% - VAT high rate, excluding (purchase)</t>
+          <t>Ticket sales outside EU</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>80001</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Advisory costs</t>
+          <t>Turnover flights</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="n">
-        <v>-12000</v>
+        <v>-6900347.94</v>
       </c>
       <c r="H87" t="n">
-        <v>2</v>
+        <v>6123</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NL VAT 21% - VAT high rate, excluding (purchase)</t>
+          <t>Ticket sales outside EU</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>80002</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Advisory costs</t>
+          <t>Turnover Hotels</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>5B</t>
-        </is>
-      </c>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="n">
-        <v>2407.5</v>
+        <v>-286249.07</v>
       </c>
       <c r="H88" t="n">
-        <v>2</v>
+        <v>721</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>NL VAT 21% - VAT high rate, excluding (purchase)</t>
+          <t>Ticket sales outside EU</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>80003</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Various office expense</t>
+          <t>Turnover Other Products</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
-        <v>-82.56</v>
+        <v>-66019.77</v>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>427</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>NL VAT 21% - VAT high rate, excluding (purchase)</t>
+          <t>Ticket sales outside EU</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Various office expense</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>5B</t>
-        </is>
-      </c>
+          <t>Turnover Saas montly fees</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
-        <v>302.68</v>
+        <v>-283972.49</v>
       </c>
       <c r="H90" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
@@ -3441,21 +3429,25 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>81001</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Cashback accruals</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr"/>
+          <t>Markup Flights</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
-        <v>-26775.54</v>
+        <v>-342590.31</v>
       </c>
       <c r="H91" t="n">
-        <v>556</v>
+        <v>5991</v>
       </c>
     </row>
     <row r="92">
@@ -3471,21 +3463,25 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>80001</t>
+          <t>81002</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Turnover flights</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr"/>
+          <t>Markup Hotels</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
-        <v>-6900347.94</v>
+        <v>-39581.77</v>
       </c>
       <c r="H92" t="n">
-        <v>6123</v>
+        <v>720</v>
       </c>
     </row>
     <row r="93">
@@ -3501,21 +3497,25 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>80002</t>
+          <t>81003</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Turnover Hotels</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr"/>
+          <t>Markup Other Products</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="n">
-        <v>-286249.07</v>
+        <v>-9536.469999999999</v>
       </c>
       <c r="H93" t="n">
-        <v>721</v>
+        <v>451</v>
       </c>
     </row>
     <row r="94">
@@ -3531,21 +3531,25 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>80003</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Turnover Other Products</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr"/>
+          <t>FX markup</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="n">
-        <v>-66019.77</v>
+        <v>-28212.67</v>
       </c>
       <c r="H94" t="n">
-        <v>427</v>
+        <v>4699</v>
       </c>
     </row>
     <row r="95">
@@ -3561,12 +3565,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Turnover Saas montly fees</t>
+          <t>Consolidator markup</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3576,10 +3580,10 @@
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
-        <v>-283972.49</v>
+        <v>-5684.83</v>
       </c>
       <c r="H95" t="n">
-        <v>5</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="96">
@@ -3595,12 +3599,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>81001</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Markup Flights</t>
+          <t>GDS incentive compensation markup</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3610,10 +3614,10 @@
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
-        <v>-330588.97</v>
+        <v>-15823.69</v>
       </c>
       <c r="H96" t="n">
-        <v>5549</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="97">
@@ -3629,29 +3633,21 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>81001</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Markup Flights</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+          <t>Revenue from rebooking price differences</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
-        <v>-12001.34</v>
+        <v>-6031.14</v>
       </c>
       <c r="H97" t="n">
-        <v>442</v>
+        <v>45</v>
       </c>
     </row>
     <row r="98">
@@ -3667,25 +3663,21 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>81002</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Markup Hotels</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
+          <t>Positive variance - gain</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
-        <v>-38296.77</v>
+        <v>-4233.86</v>
       </c>
       <c r="H98" t="n">
-        <v>659</v>
+        <v>4915</v>
       </c>
     </row>
     <row r="99">
@@ -3701,29 +3693,21 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>81002</t>
+          <t>9040</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Markup Hotels</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
+          <t>FX difference - negative</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
-        <v>-1285</v>
+        <v>47.9</v>
       </c>
       <c r="H99" t="n">
-        <v>61</v>
+        <v>18</v>
       </c>
     </row>
     <row r="100">
@@ -3739,190 +3723,162 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>81003</t>
+          <t>9041</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Markup Other Products</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
+          <t>FX difference - positive</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="n">
-        <v>-8642.48</v>
+        <v>-242.4</v>
       </c>
       <c r="H100" t="n">
-        <v>376</v>
+        <v>35</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Ticket sales outside EU</t>
+          <t>Ticket Sales within EU</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>81003</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Markup Other Products</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
+          <t>Cashback accruals</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="n">
-        <v>-893.99</v>
+        <v>-154645.16</v>
       </c>
       <c r="H101" t="n">
-        <v>75</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Ticket sales outside EU</t>
+          <t>Ticket Sales within EU</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>80001</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>FX markup</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
+          <t>Turnover flights</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="n">
-        <v>-28212.67</v>
+        <v>-7865577.82</v>
       </c>
       <c r="H102" t="n">
-        <v>4699</v>
+        <v>7354</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Ticket sales outside EU</t>
+          <t>Ticket Sales within EU</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>80002</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Consolidator markup</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
+          <t>Turnover Hotels</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="n">
-        <v>-5371.99</v>
+        <v>-301706.24</v>
       </c>
       <c r="H103" t="n">
-        <v>2219</v>
+        <v>954</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ticket sales outside EU</t>
+          <t>Ticket Sales within EU</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>80003</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Consolidator markup</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+          <t>Turnover Other Products</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
       <c r="G104" t="n">
-        <v>-312.84</v>
+        <v>-131837.53</v>
       </c>
       <c r="H104" t="n">
-        <v>205</v>
+        <v>695</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Ticket sales outside EU</t>
+          <t>Ticket Sales within EU</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>GDS incentive compensation markup</t>
+          <t>Turnover Saas montly fees</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -3930,33 +3886,37 @@
           <t>Margin</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
       <c r="G105" t="n">
-        <v>-15086.9</v>
+        <v>-2409</v>
       </c>
       <c r="H105" t="n">
-        <v>1830</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ticket sales outside EU</t>
+          <t>Ticket Sales within EU</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>GDS incentive compensation markup</t>
+          <t>GDS incentives</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -3966,134 +3926,166 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>1E</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>-736.79</v>
+        <v>-209365.74</v>
       </c>
       <c r="H106" t="n">
-        <v>130</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ticket sales outside EU</t>
+          <t>Ticket Sales within EU</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>81001</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Revenue from rebooking price differences</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
+          <t>Markup Flights</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G107" t="n">
-        <v>-6031.14</v>
+        <v>-39622.62</v>
       </c>
       <c r="H107" t="n">
-        <v>45</v>
+        <v>273</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Ticket sales outside EU</t>
+          <t>Ticket Sales within EU</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>81001</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Positive variance - gain</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
+          <t>Markup Flights</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
       <c r="G108" t="n">
-        <v>-4233.86</v>
+        <v>-429204.31</v>
       </c>
       <c r="H108" t="n">
-        <v>4915</v>
+        <v>6925</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ticket sales outside EU</t>
+          <t>Ticket Sales within EU</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>9040</t>
+          <t>81002</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>FX difference - negative</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
+          <t>Markup Hotels</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G109" t="n">
-        <v>47.9</v>
+        <v>-3855.64</v>
       </c>
       <c r="H109" t="n">
-        <v>18</v>
+        <v>109</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Ticket sales outside EU</t>
+          <t>Ticket Sales within EU</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>9041</t>
+          <t>81002</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>FX difference - positive</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
+          <t>Markup Hotels</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
       <c r="G110" t="n">
-        <v>-242.4</v>
+        <v>-38170.95</v>
       </c>
       <c r="H110" t="n">
-        <v>35</v>
+        <v>845</v>
       </c>
     </row>
     <row r="111">
@@ -4109,21 +4101,29 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>81003</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Cashback accruals</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
+          <t>Markup Other Products</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G111" t="n">
-        <v>-154645.16</v>
+        <v>-641.17</v>
       </c>
       <c r="H111" t="n">
-        <v>1061</v>
+        <v>41</v>
       </c>
     </row>
     <row r="112">
@@ -4139,21 +4139,29 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>80001</t>
+          <t>81003</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Turnover flights</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
+          <t>Markup Other Products</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
       <c r="G112" t="n">
-        <v>-7865577.82</v>
+        <v>-16989.31</v>
       </c>
       <c r="H112" t="n">
-        <v>7354</v>
+        <v>662</v>
       </c>
     </row>
     <row r="113">
@@ -4169,21 +4177,29 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>80002</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Turnover Hotels</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
+          <t>FX markup</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G113" t="n">
-        <v>-301706.24</v>
+        <v>-4565.68</v>
       </c>
       <c r="H113" t="n">
-        <v>954</v>
+        <v>171</v>
       </c>
     </row>
     <row r="114">
@@ -4199,21 +4215,29 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>80003</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Turnover Other Products</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
+          <t>FX markup</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
       <c r="G114" t="n">
-        <v>-131837.53</v>
+        <v>-12445.98</v>
       </c>
       <c r="H114" t="n">
-        <v>695</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="115">
@@ -4229,12 +4253,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Turnover Saas montly fees</t>
+          <t>Consolidator markup</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4244,14 +4268,14 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>1E</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>-2409</v>
+        <v>-708.01</v>
       </c>
       <c r="H115" t="n">
-        <v>1</v>
+        <v>154</v>
       </c>
     </row>
     <row r="116">
@@ -4267,12 +4291,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>GDS incentives</t>
+          <t>Consolidator markup</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4282,14 +4306,14 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>1E</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>-209365.74</v>
+        <v>-8509.77</v>
       </c>
       <c r="H116" t="n">
-        <v>5</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="117">
@@ -4305,12 +4329,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>81001</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Markup Flights</t>
+          <t>GDS incentive compensation markup</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4318,12 +4342,16 @@
           <t>Margin</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G117" t="n">
-        <v>-30075.09</v>
+        <v>-3632.35</v>
       </c>
       <c r="H117" t="n">
-        <v>128</v>
+        <v>149</v>
       </c>
     </row>
     <row r="118">
@@ -4339,12 +4367,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>81001</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Markup Flights</t>
+          <t>GDS incentive compensation markup</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4354,14 +4382,14 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>1E</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>-438751.84</v>
+        <v>-24295.35</v>
       </c>
       <c r="H118" t="n">
-        <v>7070</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="119">
@@ -4377,25 +4405,21 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>81002</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Markup Hotels</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
+          <t>Revenue from rebooking price differences</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="n">
-        <v>-2427.64</v>
+        <v>-5163.17</v>
       </c>
       <c r="H119" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="120">
@@ -4411,29 +4435,21 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>81002</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Markup Hotels</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+          <t>Positive variance - gain</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
       <c r="G120" t="n">
-        <v>-1428</v>
+        <v>-7834.19</v>
       </c>
       <c r="H120" t="n">
-        <v>70</v>
+        <v>7049</v>
       </c>
     </row>
     <row r="121">
@@ -4449,29 +4465,21 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>81002</t>
+          <t>9040</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Markup Hotels</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
+          <t>FX difference - negative</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
-        <v>-38170.95</v>
+        <v>4304.45</v>
       </c>
       <c r="H121" t="n">
-        <v>845</v>
+        <v>61</v>
       </c>
     </row>
     <row r="122">
@@ -4487,156 +4495,132 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>81003</t>
+          <t>9041</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Markup Other Products</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
+          <t>FX difference - positive</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="n">
-        <v>-155.28</v>
+        <v>-32.06</v>
       </c>
       <c r="H122" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>91</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ticket Sales within EU</t>
+          <t>Ticket purchases EU</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>81003</t>
+          <t>7223</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Markup Other Products</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+          <t>Incidentals, errors, ADM penalties</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
       <c r="G123" t="n">
-        <v>-485.89</v>
+        <v>5267.19</v>
       </c>
       <c r="H123" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ticket Sales within EU</t>
+          <t>Ancill services NL</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>81003</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Markup Other Products</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
+          <t>VAT payable Low</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
       <c r="G124" t="n">
-        <v>-16989.31</v>
+        <v>-6885.65</v>
       </c>
       <c r="H124" t="n">
-        <v>662</v>
+        <v>317</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ticket Sales within EU</t>
+          <t>Ancill services NL</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>80002</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>FX markup</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
+          <t>Turnover Hotels</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="n">
-        <v>-17011.66</v>
+        <v>-67109.02</v>
       </c>
       <c r="H125" t="n">
-        <v>1400</v>
+        <v>316</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ticket Sales within EU</t>
+          <t>Ancill services NL</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>81002</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Consolidator markup</t>
+          <t>Markup Hotels</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -4644,353 +4628,377 @@
           <t>Margin</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
       <c r="G126" t="n">
-        <v>-615.59</v>
+        <v>-9337.98</v>
       </c>
       <c r="H126" t="n">
-        <v>93</v>
+        <v>316</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ticket Sales within EU</t>
+          <t>Ancill services NL</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>9040</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Consolidator markup</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+          <t>FX difference - negative</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
       <c r="G127" t="n">
-        <v>-8602.190000000001</v>
+        <v>-60.17</v>
       </c>
       <c r="H127" t="n">
-        <v>2734</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>97</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Ticket Sales within EU</t>
+          <t>Ancill services purchases outside EU low (9%)</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>GDS incentive compensation markup</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
+          <t>Bookings cost of sale suspense</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="n">
-        <v>-3312.6</v>
+        <v>862238.71</v>
       </c>
       <c r="H128" t="n">
-        <v>94</v>
+        <v>10</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>97</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Ticket Sales within EU</t>
+          <t>Ancill services purchases outside EU low (9%)</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>9029</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>GDS incentive compensation markup</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+          <t>Gillion Interest</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
       <c r="G129" t="n">
-        <v>-24615.1</v>
+        <v>40473</v>
       </c>
       <c r="H129" t="n">
-        <v>2388</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>FEU</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Ticket Sales within EU</t>
+          <t>Flight Margin EU (0%)</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Revenue from rebooking price differences</t>
+          <t>Cashback accruals</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G130" t="n">
-        <v>-5163.17</v>
+        <v>-32341.7</v>
       </c>
       <c r="H130" t="n">
-        <v>32</v>
+        <v>326</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>FEU</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Ticket Sales within EU</t>
+          <t>Flight Margin EU (0%)</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>81001</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Positive variance - gain</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
+          <t>Markup Flights</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G131" t="n">
-        <v>-7834.19</v>
+        <v>-119346.51</v>
       </c>
       <c r="H131" t="n">
-        <v>7049</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>FEU</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Ticket Sales within EU</t>
+          <t>Flight Margin EU (0%)</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>9040</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>FX difference - negative</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
+          <t>FX markup</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G132" t="n">
-        <v>4304.45</v>
+        <v>-3373.07</v>
       </c>
       <c r="H132" t="n">
-        <v>61</v>
+        <v>309</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>FEU</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ticket Sales within EU</t>
+          <t>Flight Margin EU (0%)</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>9041</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>FX difference - positive</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
+          <t>Consolidator markup</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G133" t="n">
-        <v>-32.06</v>
+        <v>-2198.29</v>
       </c>
       <c r="H133" t="n">
-        <v>20</v>
+        <v>782</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>FEU</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Ticket purchases EU</t>
+          <t>Flight Margin EU (0%)</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>7223</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Incidentals, errors, ADM penalties</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
+          <t>GDS incentive compensation markup</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G134" t="n">
-        <v>5267.19</v>
+        <v>-5915.43</v>
       </c>
       <c r="H134" t="n">
-        <v>1</v>
+        <v>652</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>FEU</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ancill services NL</t>
+          <t>Flight Margin EU (0%)</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VAT payable Low</t>
+          <t>Revenue from rebooking price differences</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G135" t="n">
-        <v>-6885.65</v>
+        <v>-108.08</v>
       </c>
       <c r="H135" t="n">
-        <v>317</v>
+        <v>4</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ancill services NL</t>
+          <t>VAT Exempt - financial services</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>80002</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Turnover Hotels</t>
+          <t>Insurance costs Illness</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="n">
-        <v>-67109.02</v>
+        <v>294.5</v>
       </c>
       <c r="H136" t="n">
-        <v>316</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ancill services NL</t>
+          <t>VAT Exempt - financial services</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>81002</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Markup Hotels</t>
+          <t>GDS incentives</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -5000,405 +5008,369 @@
       </c>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="n">
-        <v>-175</v>
+        <v>-9218.35</v>
       </c>
       <c r="H137" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ancill services NL</t>
+          <t>VAT Exempt</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>81002</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Markup Hotels</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>1A</t>
-        </is>
-      </c>
+          <t>Amex Credit card costs</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
       <c r="G138" t="n">
-        <v>-9162.98</v>
+        <v>-7719.08</v>
       </c>
       <c r="H138" t="n">
-        <v>304</v>
+        <v>245</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Ancill services NL</t>
+          <t>VAT Exempt - financial services</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>9040</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>FX difference - negative</t>
+          <t>Amex Credit card costs</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="n">
-        <v>-60.17</v>
+        <v>-276.1</v>
       </c>
       <c r="H139" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Ancill services purchases outside EU low (9%)</t>
+          <t>VAT Exempt</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Bookings cost of sale suspense</t>
+          <t>Ecommpay fee EUR</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="n">
-        <v>862238.71</v>
+        <v>-1110.56</v>
       </c>
       <c r="H140" t="n">
-        <v>10</v>
+        <v>169</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Ancill services purchases outside EU low (9%)</t>
+          <t>VAT Exempt - financial services</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Gillion Interest</t>
+          <t>Ecommpay fee EUR</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="n">
-        <v>40473</v>
+        <v>-48.51</v>
       </c>
       <c r="H141" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>FEU</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Flight Margin EU (0%)</t>
+          <t>VAT Exempt</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>8113</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Cashback accruals</t>
+          <t>Ecommpay fee USD</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+      <c r="F142" t="inlineStr"/>
       <c r="G142" t="n">
-        <v>-32341.7</v>
+        <v>-34.01</v>
       </c>
       <c r="H142" t="n">
-        <v>326</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>FEU</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Flight Margin EU (0%)</t>
+          <t>VAT Exempt</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>81001</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Markup Flights</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+          <t>Payment method fees ancillary services NL Corporate</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
       <c r="G143" t="n">
-        <v>-119346.51</v>
+        <v>-291.82</v>
       </c>
       <c r="H143" t="n">
-        <v>2031</v>
+        <v>49</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>FEU</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Flight Margin EU (0%)</t>
+          <t>VAT Exempt - financial services</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>FX markup</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
+          <t>Payment method fees ancillary services NL Corporate</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="n">
-        <v>-3373.07</v>
+        <v>-2.97</v>
       </c>
       <c r="H144" t="n">
-        <v>309</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>FEU</t>
+          <t>FWW</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Flight Margin EU (0%)</t>
+          <t>Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Consolidator markup</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+          <t>Cashback accruals</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
       <c r="G145" t="n">
-        <v>-2198.29</v>
+        <v>-5491.87</v>
       </c>
       <c r="H145" t="n">
-        <v>782</v>
+        <v>93</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>FEU</t>
+          <t>FWW</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Flight Margin EU (0%)</t>
+          <t>Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>80001</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>GDS incentive compensation markup</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+          <t>Turnover flights</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
       <c r="G146" t="n">
-        <v>-5915.43</v>
+        <v>-1319018.6</v>
       </c>
       <c r="H146" t="n">
-        <v>652</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>FEU</t>
+          <t>FWW</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Flight Margin EU (0%)</t>
+          <t>Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>81001</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Revenue from rebooking price differences</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+          <t>Markup Flights</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
       <c r="G147" t="n">
-        <v>-108.08</v>
+        <v>-66693.53</v>
       </c>
       <c r="H147" t="n">
-        <v>4</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>FWW</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>VAT Exempt - financial services</t>
+          <t>Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Insurance costs Illness</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr"/>
+          <t>FX markup</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="n">
-        <v>294.5</v>
+        <v>-5477.37</v>
       </c>
       <c r="H148" t="n">
-        <v>1</v>
+        <v>842</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>FWW</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>VAT Exempt - financial services</t>
+          <t>Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>GDS incentives</t>
+          <t>Consolidator markup</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5406,223 +5378,263 @@
           <t>Margin</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+      <c r="F149" t="inlineStr"/>
       <c r="G149" t="n">
-        <v>-9218.35</v>
+        <v>-1013.38</v>
       </c>
       <c r="H149" t="n">
-        <v>1</v>
+        <v>475</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>FWW</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>VAT Exempt</t>
+          <t>Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Amex Credit card costs</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr"/>
+          <t>GDS incentive compensation markup</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="n">
-        <v>-7719.08</v>
+        <v>-3062.05</v>
       </c>
       <c r="H150" t="n">
-        <v>245</v>
+        <v>400</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>FWW</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>VAT Exempt - financial services</t>
+          <t>Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Amex Credit card costs</t>
+          <t>Revenue from rebooking price differences</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="n">
-        <v>-276.1</v>
+        <v>205.61</v>
       </c>
       <c r="H151" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>NEU</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>VAT Exempt</t>
+          <t>EU Sales Reverse Charge</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8021</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Ecommpay fee EUR</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
+          <t>GDS incentives</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
       <c r="G152" t="n">
-        <v>-1110.56</v>
+        <v>-18917.58</v>
       </c>
       <c r="H152" t="n">
-        <v>169</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>NEU</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>VAT Exempt - financial services</t>
+          <t>EU Sales Reverse Charge</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8090</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Ecommpay fee EUR</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
+          <t>Platform subscription fee</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
       <c r="G153" t="n">
-        <v>-48.51</v>
+        <v>-500</v>
       </c>
       <c r="H153" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>NEU</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>VAT Exempt</t>
+          <t>EU Sales Reverse Charge</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>8113</t>
+          <t>8091</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Ecommpay fee USD</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
+          <t>Minimum booking fee</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
       <c r="G154" t="n">
-        <v>-34.01</v>
+        <v>-117.69</v>
       </c>
       <c r="H154" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>NEU</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>VAT Exempt</t>
+          <t>EU Sales Reverse Charge</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>81003</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Payment method fees ancillary services NL Corporate</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
+          <t>Markup Other Products</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
       <c r="G155" t="n">
-        <v>-291.82</v>
+        <v>-25</v>
       </c>
       <c r="H155" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>NEX</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>VAT Exempt - financial services</t>
+          <t>Non Flight Margin 0%</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>8090</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Payment method fees ancillary services NL Corporate</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
+          <t>Platform subscription fee</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G156" t="n">
-        <v>-2.97</v>
+        <v>-250</v>
       </c>
       <c r="H156" t="n">
         <v>1</v>
@@ -5631,82 +5643,94 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>FWW</t>
+          <t>NEX</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Flight Margin Non-EU</t>
+          <t>Non Flight Margin 0%</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>81003</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Cashback accruals</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
+          <t>Markup Other Products</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G157" t="n">
-        <v>-5491.87</v>
+        <v>-50</v>
       </c>
       <c r="H157" t="n">
-        <v>93</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>FWW</t>
+          <t>NNL</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Flight Margin Non-EU</t>
+          <t>Domestic Sales High (21%)</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>80001</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Turnover flights</t>
+          <t>VAT payable High</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr"/>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
       <c r="G158" t="n">
-        <v>-1319018.6</v>
+        <v>-26.25</v>
       </c>
       <c r="H158" t="n">
-        <v>1149</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>FWW</t>
+          <t>NNL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Flight Margin Non-EU</t>
+          <t>Domestic Sales High (21%)</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>81001</t>
+          <t>81003</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Markup Flights</t>
+          <t>Markup Other Products</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -5714,101 +5738,97 @@
           <t>Margin</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr"/>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
       <c r="G159" t="n">
-        <v>-66693.53</v>
+        <v>-125</v>
       </c>
       <c r="H159" t="n">
-        <v>1148</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>FWW</t>
+          <t>NWW</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Flight Margin Non-EU</t>
+          <t>Non-Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>80002</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>FX markup</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
+          <t>Turnover Hotels</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="n">
-        <v>-5477.37</v>
+        <v>-46083.51</v>
       </c>
       <c r="H160" t="n">
-        <v>842</v>
+        <v>134</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>FWW</t>
+          <t>NWW</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Flight Margin Non-EU</t>
+          <t>Non-Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>80003</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Consolidator markup</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
+          <t>Turnover Other Products</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="n">
-        <v>-1013.38</v>
+        <v>-881.5</v>
       </c>
       <c r="H161" t="n">
-        <v>475</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>FWW</t>
+          <t>NWW</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Flight Margin Non-EU</t>
+          <t>Non-Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8091</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>GDS incentive compensation markup</t>
+          <t>Minimum booking fee</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -5818,61 +5838,65 @@
       </c>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="n">
-        <v>-3062.05</v>
+        <v>-2249.36</v>
       </c>
       <c r="H162" t="n">
-        <v>400</v>
+        <v>22</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>FWW</t>
+          <t>NWW</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Flight Margin Non-EU</t>
+          <t>Non-Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>81002</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Revenue from rebooking price differences</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr"/>
+          <t>Markup Hotels</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="n">
-        <v>205.61</v>
+        <v>-1.15</v>
       </c>
       <c r="H163" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>NEU</t>
+          <t>NWW</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EU Sales Reverse Charge</t>
+          <t>Non-Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>81003</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>GDS incentives</t>
+          <t>Markup Other Products</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -5880,189 +5904,153 @@
           <t>Margin</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+      <c r="F164" t="inlineStr"/>
       <c r="G164" t="n">
-        <v>-18917.58</v>
+        <v>-91.23999999999999</v>
       </c>
       <c r="H164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>NEU</t>
+          <t>NWW</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EU Sales Reverse Charge</t>
+          <t>Non-Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>8090</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Platform subscription fee</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
+          <t>Amex Credit card costs</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
       <c r="G165" t="n">
-        <v>-500</v>
+        <v>-4157.92</v>
       </c>
       <c r="H165" t="n">
-        <v>2</v>
+        <v>167</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>NEU</t>
+          <t>NWW</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>EU Sales Reverse Charge</t>
+          <t>Non-Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>8091</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Minimum booking fee</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
+          <t>Ecommpay fee EUR</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
       <c r="G166" t="n">
-        <v>-117.69</v>
+        <v>-1873.3</v>
       </c>
       <c r="H166" t="n">
-        <v>9</v>
+        <v>146</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>NEU</t>
+          <t>NWW</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>EU Sales Reverse Charge</t>
+          <t>Non-Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>81003</t>
+          <t>8113</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Markup Other Products</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
+          <t>Ecommpay fee USD</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
       <c r="G167" t="n">
-        <v>-25</v>
+        <v>-3748.14</v>
       </c>
       <c r="H167" t="n">
-        <v>1</v>
+        <v>126</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>NEX</t>
+          <t>NWW</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Non Flight Margin 0%</t>
+          <t>Non-Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>8090</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Platform subscription fee</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+          <t>Ecommpay fee GBP</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
       <c r="G168" t="n">
-        <v>-250</v>
+        <v>-787.22</v>
       </c>
       <c r="H168" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>NEX</t>
+          <t>NWW</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Non Flight Margin 0%</t>
+          <t>Non-Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>81003</t>
+          <t>82002</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Markup Other Products</t>
+          <t>Commission Hotels</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -6070,99 +6058,83 @@
           <t>Margin</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>1E</t>
-        </is>
-      </c>
+      <c r="F169" t="inlineStr"/>
       <c r="G169" t="n">
-        <v>-50</v>
+        <v>-6591.13</v>
       </c>
       <c r="H169" t="n">
-        <v>2</v>
+        <v>133</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>NNL</t>
+          <t>NWW</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Domestic Sales High (21%)</t>
+          <t>Non-Flight Margin Non-EU</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VAT payable High</t>
+          <t>Payment method fees ancillary services NL Corporate</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>1A</t>
-        </is>
-      </c>
+      <c r="F170" t="inlineStr"/>
       <c r="G170" t="n">
-        <v>-26.25</v>
+        <v>-679.77</v>
       </c>
       <c r="H170" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>NNL</t>
+          <t>PAS</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Domestic Sales High (21%)</t>
+          <t>Paid on behalf of customer</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>81003</t>
+          <t>80001</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Markup Other Products</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>1A</t>
-        </is>
-      </c>
+          <t>Turnover flights</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
       <c r="G171" t="n">
-        <v>-125</v>
+        <v>-2106220.81</v>
       </c>
       <c r="H171" t="n">
-        <v>2</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>NWW</t>
+          <t>PAS</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Non-Flight Margin Non-EU</t>
+          <t>Paid on behalf of customer</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6178,21 +6150,21 @@
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="n">
-        <v>-46083.51</v>
+        <v>-80905.00999999999</v>
       </c>
       <c r="H172" t="n">
-        <v>134</v>
+        <v>256</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>NWW</t>
+          <t>PAS</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Non-Flight Margin Non-EU</t>
+          <t>Paid on behalf of customer</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6208,31 +6180,31 @@
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="n">
-        <v>-881.5</v>
+        <v>-1286.28</v>
       </c>
       <c r="H173" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>NWW</t>
+          <t>PAS</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Non-Flight Margin Non-EU</t>
+          <t>Paid on behalf of customer</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>8091</t>
+          <t>82002</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Minimum booking fee</t>
+          <t>Commission Hotels</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -6242,31 +6214,31 @@
       </c>
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="n">
-        <v>-2249.36</v>
+        <v>-498.39</v>
       </c>
       <c r="H174" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>NWW</t>
+          <t>PAS</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Non-Flight Margin Non-EU</t>
+          <t>Paid on behalf of customer</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>81002</t>
+          <t>82002</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Markup Hotels</t>
+          <t>Commission Hotels</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -6274,33 +6246,37 @@
           <t>Margin</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
       <c r="G175" t="n">
-        <v>-1.15</v>
+        <v>-2304</v>
       </c>
       <c r="H175" t="n">
-        <v>1</v>
+        <v>77</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>NWW</t>
+          <t>PAS</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Non-Flight Margin Non-EU</t>
+          <t>Paid on behalf of customer</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>81003</t>
+          <t>82002</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Markup Other Products</t>
+          <t>Commission Hotels</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -6308,283 +6284,315 @@
           <t>Margin</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>1E</t>
+        </is>
+      </c>
       <c r="G176" t="n">
-        <v>-91.23999999999999</v>
+        <v>-298</v>
       </c>
       <c r="H176" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>NWW</t>
+          <t>PAS</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Non-Flight Margin Non-EU</t>
+          <t>Paid on behalf of customer</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>82002</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Amex Credit card costs</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
+          <t>Commission Hotels</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
       <c r="G177" t="n">
-        <v>-4157.92</v>
+        <v>-8206.57</v>
       </c>
       <c r="H177" t="n">
-        <v>167</v>
+        <v>150</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>NWW</t>
+          <t>UEU</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Non-Flight Margin Non-EU</t>
+          <t>European Reverse Charge</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>40751</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Ecommpay fee EUR</t>
+          <t>Outsourced personnel - IT Team</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>4B, 5B</t>
+        </is>
+      </c>
       <c r="G178" t="n">
-        <v>-1873.3</v>
+        <v>5150</v>
       </c>
       <c r="H178" t="n">
-        <v>146</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>NWW</t>
+          <t>UEU</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Non-Flight Margin Non-EU</t>
+          <t>European Reverse Charge</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>8113</t>
+          <t>40755</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Ecommpay fee USD</t>
+          <t>Outsourced personnel - Product Team</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>4B, 5B</t>
+        </is>
+      </c>
       <c r="G179" t="n">
-        <v>-3748.14</v>
+        <v>4200</v>
       </c>
       <c r="H179" t="n">
-        <v>126</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>NWW</t>
+          <t>UN9</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Non-Flight Margin Non-EU</t>
+          <t>Domestic Purchases Low (9%)</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>8114</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Ecommpay fee GBP</t>
+          <t>Vat Receivable (low)</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="n">
-        <v>-787.22</v>
+        <v>222.35</v>
       </c>
       <c r="H180" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>NWW</t>
+          <t>UN9</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Non-Flight Margin Non-EU</t>
+          <t>Domestic Purchases Low (9%)</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>82002</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Commission Hotels</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr"/>
+          <t>Other Personnel Costs</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>5B</t>
+        </is>
+      </c>
       <c r="G181" t="n">
-        <v>-6591.13</v>
+        <v>2470.62</v>
       </c>
       <c r="H181" t="n">
-        <v>133</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>NWW</t>
+          <t>UNL</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Non-Flight Margin Non-EU</t>
+          <t>Domestic Purchases High (21%)</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Payment method fees ancillary services NL Corporate</t>
+          <t>Vat Receivable (high)</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="n">
-        <v>-679.77</v>
+        <v>423.5</v>
       </c>
       <c r="H182" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>PAS</t>
+          <t>UNL</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Paid on behalf of customer</t>
+          <t>Domestic Purchases High (21%)</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>80001</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Turnover flights</t>
+          <t>Other Personnel Costs</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>5B</t>
+        </is>
+      </c>
       <c r="G183" t="n">
-        <v>-2106220.81</v>
+        <v>2016.67</v>
       </c>
       <c r="H183" t="n">
-        <v>2047</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>PAS</t>
+          <t>UWW</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Paid on behalf of customer</t>
+          <t>Non-EU Purchases Reverse Charge</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>80002</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Turnover Hotels</t>
+          <t>Cashback accruals</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>4A, 5B</t>
+        </is>
+      </c>
       <c r="G184" t="n">
-        <v>-80905.00999999999</v>
+        <v>14490</v>
       </c>
       <c r="H184" t="n">
-        <v>256</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>PAS</t>
+          <t>UWW</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Paid on behalf of customer</t>
+          <t>Non-EU Purchases Reverse Charge</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>80003</t>
+          <t>40751</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Turnover Other Products</t>
+          <t>Outsourced personnel - IT Team</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>4A, 5B</t>
+        </is>
+      </c>
       <c r="G185" t="n">
-        <v>-1286.28</v>
+        <v>31075</v>
       </c>
       <c r="H185" t="n">
         <v>6</v>
@@ -6593,616 +6601,204 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>PAS</t>
+          <t>UWW</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Paid on behalf of customer</t>
+          <t>Non-EU Purchases Reverse Charge</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>82002</t>
+          <t>40752</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Commission Hotels</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr"/>
+          <t>Outsourced personnel - Finance Team</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>4A, 5B</t>
+        </is>
+      </c>
       <c r="G186" t="n">
-        <v>-498.39</v>
+        <v>1750</v>
       </c>
       <c r="H186" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>PAS</t>
+          <t>UWW</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Paid on behalf of customer</t>
+          <t>Non-EU Purchases Reverse Charge</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>82002</t>
+          <t>40754</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Commission Hotels</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
+          <t>Outsourced personnel - Operations Team</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>1A</t>
+          <t>4A, 5B</t>
         </is>
       </c>
       <c r="G187" t="n">
-        <v>-2304</v>
+        <v>6451.69</v>
       </c>
       <c r="H187" t="n">
-        <v>77</v>
+        <v>4</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>PAS</t>
+          <t>UWW</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Paid on behalf of customer</t>
+          <t>Non-EU Purchases Reverse Charge</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>82002</t>
+          <t>40755</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Commission Hotels</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
+          <t>Outsourced personnel - Product Team</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
-          <t>1E</t>
+          <t>4A, 5B</t>
         </is>
       </c>
       <c r="G188" t="n">
-        <v>-298</v>
+        <v>10400</v>
       </c>
       <c r="H188" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>PAS</t>
+          <t>UWW</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Paid on behalf of customer</t>
+          <t>Non-EU Purchases Reverse Charge</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>82002</t>
+          <t>40757</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Commission Hotels</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
+          <t>Outsourced personnel - Customer Success Team</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>4A, 5B</t>
         </is>
       </c>
       <c r="G189" t="n">
-        <v>-8206.57</v>
+        <v>3855</v>
       </c>
       <c r="H189" t="n">
-        <v>150</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>UEU</t>
+          <t>UWW</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>European Reverse Charge</t>
+          <t>Non-EU Purchases Reverse Charge</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>40751</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Outsourced personnel - IT Team</t>
+          <t>Conferences and exhibitions</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
-          <t>4B, 5B</t>
+          <t>4A, 5B</t>
         </is>
       </c>
       <c r="G190" t="n">
-        <v>5150</v>
+        <v>12877.03</v>
       </c>
       <c r="H190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>UEU</t>
+          <t>UWW</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>European Reverse Charge</t>
+          <t>Non-EU Purchases Reverse Charge</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>40755</t>
+          <t>4856</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Outsourced personnel - Product Team</t>
+          <t>Advisory costs</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
-          <t>4B, 5B</t>
+          <t>4A, 5B</t>
         </is>
       </c>
       <c r="G191" t="n">
-        <v>4200</v>
+        <v>6571.35</v>
       </c>
       <c r="H191" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>UN9</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Domestic Purchases Low (9%)</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>Vat Receivable (low)</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="n">
-        <v>222.35</v>
-      </c>
-      <c r="H192" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>UN9</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Domestic Purchases Low (9%)</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>4074</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>Other Personnel Costs</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>5B</t>
-        </is>
-      </c>
-      <c r="G193" t="n">
-        <v>2470.62</v>
-      </c>
-      <c r="H193" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>UNL</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Domestic Purchases High (21%)</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>1511</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>Vat Receivable (high)</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr"/>
-      <c r="F194" t="inlineStr"/>
-      <c r="G194" t="n">
-        <v>423.5</v>
-      </c>
-      <c r="H194" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>UNL</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Domestic Purchases High (21%)</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>4074</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>Other Personnel Costs</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>5B</t>
-        </is>
-      </c>
-      <c r="G195" t="n">
-        <v>2016.67</v>
-      </c>
-      <c r="H195" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>UWW</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Non-EU Purchases Reverse Charge</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>1602</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>Cashback accruals</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>4A, 5B</t>
-        </is>
-      </c>
-      <c r="G196" t="n">
-        <v>14490</v>
-      </c>
-      <c r="H196" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>UWW</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Non-EU Purchases Reverse Charge</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>40751</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>Outsourced personnel - IT Team</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>4A, 5B</t>
-        </is>
-      </c>
-      <c r="G197" t="n">
-        <v>31075</v>
-      </c>
-      <c r="H197" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>UWW</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Non-EU Purchases Reverse Charge</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>40752</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>Outsourced personnel - Finance Team</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>4A, 5B</t>
-        </is>
-      </c>
-      <c r="G198" t="n">
-        <v>1750</v>
-      </c>
-      <c r="H198" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>UWW</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Non-EU Purchases Reverse Charge</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>40754</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>Outsourced personnel - Operations Team</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>4A, 5B</t>
-        </is>
-      </c>
-      <c r="G199" t="n">
-        <v>6451.69</v>
-      </c>
-      <c r="H199" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>UWW</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Non-EU Purchases Reverse Charge</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>40755</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>Outsourced personnel - Product Team</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>4A, 5B</t>
-        </is>
-      </c>
-      <c r="G200" t="n">
-        <v>10400</v>
-      </c>
-      <c r="H200" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>UWW</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Non-EU Purchases Reverse Charge</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>40757</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>Outsourced personnel - Customer Success Team</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr"/>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>4A, 5B</t>
-        </is>
-      </c>
-      <c r="G201" t="n">
-        <v>3855</v>
-      </c>
-      <c r="H201" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>UWW</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Non-EU Purchases Reverse Charge</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>4340</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>Conferences and exhibitions</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr"/>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>4A, 5B</t>
-        </is>
-      </c>
-      <c r="G202" t="n">
-        <v>12877.03</v>
-      </c>
-      <c r="H202" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>UWW</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>Non-EU Purchases Reverse Charge</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>4856</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>Advisory costs</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr"/>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>4A, 5B</t>
-        </is>
-      </c>
-      <c r="G203" t="n">
-        <v>6571.35</v>
-      </c>
-      <c r="H203" t="n">
         <v>1</v>
       </c>
     </row>
